--- a/Dados-apoio/proj-2015-2019-POP-GERAL-RIPSA.xlsx
+++ b/Dados-apoio/proj-2015-2019-POP-GERAL-RIPSA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="648">
   <si>
     <t xml:space="preserve">IBGE</t>
   </si>
@@ -31,1948 +31,1939 @@
     <t xml:space="preserve">POP_GERAL</t>
   </si>
   <si>
-    <t xml:space="preserve"> ADAMANTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ADOLFO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AGUAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AGUAS DA PRATA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AGUAS DE LINDOIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AGUAS DE SANTA BARBARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AGUAS DE SAO PEDRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AGUDOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALAMBARI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALFREDO MARCONDES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALTAIR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALTINOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALTO ALEGRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALUMINIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALVARES FLORENCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALVARES MACHADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALVARO DE CARVALHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALVINLANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AMERICANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AMERICO BRASILIENSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AMERICO DE CAMPOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AMPARO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ANALANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ANDRADINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ANGATUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ANHEMBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ANHUMAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> APARECIDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> APARECIDA D'OESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> APIAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARACARIGUAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARACATUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARACOIABA DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARAMINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARANDU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARAPEI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARARAQUARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARARAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARCO-IRIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AREALVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AREIAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AREIOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARIRANHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARTUR NOGUEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARUJA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ASPASIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ASSIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ATIBAIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AURIFLAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AVAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AVANHANDAVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AVARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BADY BASSITT</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BALBINOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BALSAMO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BANANAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARAO DE ANTONINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARBOSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARIRI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARRA BONITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARRA DO CHAPEU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARRA DO TURVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARRETOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARRINHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BARUERI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BASTOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BATATAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BAURU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BEBEDOURO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BENTO DE ABREU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BERNARDINO DE CAMPOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BERTIOGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BILAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BIRIGUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BIRITIBA MIRIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOA ESPERANCA DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOCAINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOFETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOITUVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOM JESUS DOS PERDOES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOM SUCESSO DE ITARARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BORACEIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BORBOREMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOREBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BOTUCATU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BRAGANCA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BRAUNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BREJO ALEGRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BRODOWSKI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BROTAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BURI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BURITAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BURITIZAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CABRALIA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CABREUVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CACAPAVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CACHOEIRA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CACONDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAFELANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAIABU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAIEIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAIUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAJAMAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAJATI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAJOBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAJURU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAMPINA DO MONTE ALEGRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAMPINAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAMPO LIMPO PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAMPOS DO JORDAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAMPOS NOVOS PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CANANEIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CANAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CANDIDO MOTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CANDIDO RODRIGUES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CANITAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAPAO BONITO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAPELA DO ALTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAPIVARI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CARAGUATATUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CARAPICUIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CARDOSO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CASA BRANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CASSIA DOS COQUEIROS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CASTILHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CATANDUVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CATIGUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CEDRAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CERQUEIRA CESAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CERQUILHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CESARIO LANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CHARQUEADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CLEMENTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> COLINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> COLOMBIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CONCHAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CONCHAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CORDEIROPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> COROADOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CORONEL MACEDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CORUMBATAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> COSMOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> COSMORAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> COTIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CRAVINHOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CRISTAIS PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CRUZALIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CRUZEIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CUBATAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CUNHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DESCALVADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DIADEMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DIRCE REIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DIVINOLANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DOBRADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DOIS CORREGOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DOLCINOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DOURADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DRACENA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DUARTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DUMONT</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ECHAPORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ELDORADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ELIAS FAUSTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ELISIARIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EMBAUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EMBU DAS ARTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EMBU-GUACU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EMILIANOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ENGENHEIRO COELHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ESPIRITO SANTO DO PINHAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ESPIRITO SANTO DO TURVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ESTRELA D'OESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ESTRELA DO NORTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EUCLIDES DA CUNHA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FARTURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FERNANDOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FERNANDO PRESTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FERNAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FERRAZ DE VASCONCELOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FLORA RICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FLOREAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FLORIDA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FLORINEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FRANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FRANCISCO MORATO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FRANCO DA ROCHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GABRIEL MONTEIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GALIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GARCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GASTAO VIDIGAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GAVIAO PEIXOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GENERAL SALGADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GETULINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GLICERIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUAICARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUAIMBE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUAIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUAPIACU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUAPIARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARACAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARACI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARANI D'OESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARANTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARARAPES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARAREMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARATINGUETA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUAREI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARUJA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUARULHOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUATAPARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GUZOLANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HERCULANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HOLAMBRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HORTOLANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IACANGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IACRI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IARAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IBATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IBIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IBIRAREMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IBITINGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IBIUNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ICEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IEPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IGARACU DO TIETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IGARAPAVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IGARATA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IGUAPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ILHABELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ILHA COMPRIDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ILHA SOLTEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> INDAIATUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> INDIANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> INDIAPORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> INUBIA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IPAUSSU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IPERO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IPEUNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IPIGUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IPORANGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IPUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IRACEMAPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IRAPUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IRAPURU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITABERA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAJOBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAJU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITANHAEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAOCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPECERICA DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPETININGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPEVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPEVI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPIRAPUA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPORANGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAPURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITAQUAQUECETUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITARARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITARIRI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITATIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITATINGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITIRAPINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITIRAPUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITOBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITUPEVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITUVERAVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JABORANDI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JABOTICABAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JACAREI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JACI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JACUPIRANGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JAGUARIUNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JALES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JAMBEIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JANDIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JARDINOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JARINU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JAU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JERIQUARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JOANOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JOAO RAMALHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JOSE BONIFACIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JULIO MESQUITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JUMIRIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JUNDIAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JUNQUEIROPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JUQUIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JUQUITIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LAGOINHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LARANJAL PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LAVINIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LAVRINHAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LEME</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LENCOIS PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LIMEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LINDOIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LINS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LORENA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LOURDES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LOUVEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LUCELIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LUCIANOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LUIS ANTONIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LUIZIANIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LUPERCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LUTECIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MACATUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MACAUBAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MACEDONIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MAGDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MAIRINQUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MAIRIPORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MANDURI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MARABA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MARACAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MARAPOAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MARIAPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MARILIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MARINOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MARTINOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MATAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MAUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MENDONCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MERIDIANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MESOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MIGUELOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MINEIROS DO TIETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MIRACATU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MIRA ESTRELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MIRANDOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MIRANTE DO PARANAPANEMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MIRASSOL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MIRASSOLANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MOCOCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MOGI DAS CRUZES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MOGI GUACU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MOGI MIRIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MOMBUCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONCOES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONGAGUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONTE ALEGRE DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONTE ALTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONTE APRAZIVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONTE AZUL PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONTE CASTELO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONTEIRO LOBATO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MONTE MOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MORRO AGUDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MORUNGABA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MOTUCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MURUTINGA DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NANTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NARANDIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NATIVIDADE DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NAZARE PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NEVES PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NHANDEARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NIPOA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA ALIANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA CAMPINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA CANAA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA CASTILHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA EUROPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA GRANADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA GUATAPORANGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA LUZITANIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVA ODESSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOVO HORIZONTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NUPORANGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OCAUCU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OLEO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OLIMPIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ONDA VERDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ORIENTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ORINDIUVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ORLANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OSASCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OSCAR BRESSANE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OSVALDO CRUZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OURINHOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OUROESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OURO VERDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PACAEMBU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PALESTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PALMARES PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PALMEIRA D'OESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PALMITAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PANORAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARAGUACU PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARAIBUNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARAISO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARANAPANEMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARANAPUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARAPUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARDINHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARIQUERA-ACU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARISI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PATROCINIO PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PAULICEIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PAULINIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PAULISTANIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PAULO DE FARIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEDERNEIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEDRA BELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEDRANOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEDREGULHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEDREIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEDRINHAS PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEDRO DE TOLEDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PENAPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEREIRA BARRETO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PEREIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PERUIBE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIACATU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIEDADE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PILAR DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PINDAMONHANGABA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PINDORAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PINHALZINHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIQUEROBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIQUETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRACAIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRACICABA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRAJU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRAJUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRANGI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRAPORA DO BOM JESUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRAPOZINHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRASSUNUNGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PIRATININGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PITANGUEIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PLANALTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PLATINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> POA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> POLONI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> POMPEIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PONGAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PONTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PONTALINDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PONTES GESTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> POPULINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PORANGABA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PORTO FELIZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PORTO FERREIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> POTIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> POTIRENDABA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRACINHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRADOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRAIA GRANDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRATANIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRESIDENTE ALVES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRESIDENTE BERNARDES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRESIDENTE EPITACIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRESIDENTE PRUDENTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRESIDENTE VENCESLAU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PROMISSAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> QUADRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> QUATA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> QUEIROZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> QUELUZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> QUINTANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RAFARD</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RANCHARIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> REDENCAO DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> REGENTE FEIJO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> REGINOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> REGISTRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RESTINGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO BONITO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO CORRENTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO DOS INDIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO GRANDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO PIRES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIBEIRAO PRETO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIVERSUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIFAINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RINCAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RINOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIO CLARO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIO DAS PEDRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIO GRANDE DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIOLANDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ROSANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ROSEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RUBIACEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RUBINEIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SABINO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAGRES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALES OLIVEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALESOPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALMOURAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALTINHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALTO DE PIRAPORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SALTO GRANDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANDOVALINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA ADELIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA ALBERTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA BARBARA D'OESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA BRANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA CLARA D'OESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA CRUZ DA CONCEICAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA CRUZ DA ESPERANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA CRUZ DAS PALMEIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA CRUZ DO RIO PARDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA ERNESTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA FE DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA GERTRUDES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA ISABEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA LUCIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA MARIA DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA MERCEDES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTANA DA PONTE PENSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTANA DE PARNAIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA RITA D'OESTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA RITA DO PASSA QUATRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA ROSA DE VITERBO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTA SALETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO ANASTACIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO ANDRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO ANTONIO DA ALEGRIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO ANTONIO DE POSSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO ANTONIO DO ARACANGUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO ANTONIO DO JARDIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO ANTONIO DO PINHAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTO EXPEDITO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTOPOLIS DO AGUAPEI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SANTOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO BENTO DO SAPUCAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO BERNARDO DO CAMPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO CAETANO DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO CARLOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO FRANCISCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOAO DA BOA VISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOAO DAS DUAS PONTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOAO DE IRACEMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOAO DO PAU D'ALHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOAQUIM DA BARRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOSE DA BELA VISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOSE DO BARREIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOSE DO RIO PARDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOSE DO RIO PRETO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO JOSE DOS CAMPOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO LOURENCO DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO LUIS DO PARAITINGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO MANUEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO MIGUEL ARCANJO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO PAULO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO PEDRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO PEDRO DO TURVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO ROQUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO SEBASTIAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO SEBASTIAO DA GRAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO SIMAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAO VICENTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SARAPUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SARUTAIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SEBASTIANOPOLIS DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SERRA AZUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SERRANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SERRA NEGRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SERTAOZINHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SETE BARRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SEVERINIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SILVEIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SOCORRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SOROCABA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SUD MENNUCCI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SUMARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SUZANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SUZANAPOLIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TABAPUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TABATINGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TABOAO DA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TACIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAGUAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAIACU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAIUVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAMBAU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TANABI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAPIRAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAPIRATIBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAQUARAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAQUARITINGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAQUARITUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAQUARIVAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TARABAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TARUMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TATUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TAUBATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TEJUPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TEODORO SAMPAIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TERRA ROXA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TIETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TIMBURI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TORRE DE PEDRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TORRINHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TRABIJU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TREMEMBE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TRES FRONTEIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TUIUTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TUPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TUPI PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TURIUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TURMALINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UBARANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UBATUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UBIRAJARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UCHOA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UNIAO PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> URANIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> URU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> URUPES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VALENTIM GENTIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VALINHOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VALPARAISO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VARGEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VARGEM GRANDE DO SUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VARGEM GRANDE PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VARZEA PAULISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VERA CRUZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VINHEDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VIRADOURO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VISTA ALEGRE DO ALTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VITORIA BRASIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VOTORANTIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VOTUPORANGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ZACARIAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CHAVANTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ESTIVA GERBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Fonte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:</t>
+    <t xml:space="preserve">ADAMANTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADOLFO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUAS DA PRATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUAS DE LINDOIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUAS DE SANTA BARBARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUAS DE SAO PEDRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUDOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALAMBARI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALFREDO MARCONDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTAIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTINOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTO ALEGRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALUMINIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALVARES FLORENCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALVARES MACHADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALVARO DE CARVALHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALVINLANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMERICANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMERICO BRASILIENSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMERICO DE CAMPOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMPARO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANALANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRADINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANGATUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANHEMBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANHUMAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APARECIDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APARECIDA D'OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APIAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARACARIGUAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARACATUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARACOIABA DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAMINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARANDU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAPEI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARARAQUARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARARAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARCO-IRIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AREALVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AREIAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AREIOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIRANHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARTUR NOGUEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARUJA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASPASIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATIBAIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AURIFLAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVANHANDAVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BADY BASSITT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BALBINOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BALSAMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANANAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARAO DE ANTONINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARBOSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARIRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRA BONITA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRA DO CHAPEU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRA DO TURVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRETOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRINHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARUERI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BATATAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAURU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEBEDOURO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BENTO DE ABREU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BERNARDINO DE CAMPOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BERTIOGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BILAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIRIGUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIRITIBA MIRIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOA ESPERANCA DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOCAINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOFETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOITUVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOM JESUS DOS PERDOES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOM SUCESSO DE ITARARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORACEIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORBOREMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOREBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTUCATU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRAGANCA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRAUNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BREJO ALEGRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRODOWSKI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BROTAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BURI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BURITAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BURITIZAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABRALIA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABREUVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACAPAVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACHOEIRA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACONDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAFELANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAIABU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAIEIRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAIUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAJAMAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAJATI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAJOBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAJURU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPINA DO MONTE ALEGRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPINAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPO LIMPO PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPOS DO JORDAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPOS NOVOS PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANANEIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANDIDO MOTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANDIDO RODRIGUES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANITAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPAO BONITO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPELA DO ALTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPIVARI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARAGUATATUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARAPICUIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARDOSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASA BRANCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASSIA DOS COQUEIROS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASTILHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CATANDUVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CATIGUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEDRAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERQUEIRA CESAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERQUILHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CESARIO LANGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHARQUEADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLEMENTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLOMBIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONCHAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONCHAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDEIROPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COROADOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORONEL MACEDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORUMBATAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COSMOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COSMORAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COTIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRAVINHOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTAIS PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRUZALIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRUZEIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUBATAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUNHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESCALVADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIADEMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRCE REIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIVINOLANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOBRADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOIS CORREGOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOLCINOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOURADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRACENA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUARTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUMONT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHAPORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELDORADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIAS FAUSTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELISIARIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMBAUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMBU DAS ARTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMBU-GUACU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMILIANOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGENHEIRO COELHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPIRITO SANTO DO PINHAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPIRITO SANTO DO TURVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTRELA D'OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTRELA DO NORTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUCLIDES DA CUNHA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARTURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDO PRESTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERRAZ DE VASCONCELOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLORA RICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOREAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLORIDA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLORINEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO MORATO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCO DA ROCHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIEL MONTEIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GALIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GASTAO VIDIGAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAVIAO PEIXOTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENERAL SALGADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GETULINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLICERIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUAICARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUAIMBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUAIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUAPIACU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUAPIARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARACAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARACI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARANI D'OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARANTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARARAPES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARAREMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARATINGUETA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUAREI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARUJA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARULHOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUATAPARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUZOLANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HERCULANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOLAMBRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HORTOLANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IACANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IACRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IARAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBIRAREMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBITINGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBIUNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IEPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGARACU DO TIETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGARAPAVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGARATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGUAPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILHABELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILHA COMPRIDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILHA SOLTEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDAIATUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIAPORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INUBIA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPAUSSU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPEUNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPIGUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPORANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRACEMAPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRAPUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRAPURU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITABERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAJOBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAJU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITANHAEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAOCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPECERICA DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPETININGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPEVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPEVI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPIRAPUA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPORANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAPURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAQUAQUECETUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITARARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITARIRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITATIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITATINGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITIRAPINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITIRAPUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITOBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITUPEVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITUVERAVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JABORANDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JABOTICABAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JACAREI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JACI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JACUPIRANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAGUARIUNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAMBEIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JANDIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JARDINOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JARINU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JERIQUARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOANOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO RAMALHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE BONIFACIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIO MESQUITA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUMIRIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUNDIAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUNQUEIROPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUQUIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUQUITIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAGOINHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LARANJAL PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAVINIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAVRINHAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LENCOIS PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINDOIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LORENA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOURDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOUVEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCELIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIANOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS ANTONIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZIANIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUPERCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUTECIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACATUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACAUBAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACEDONIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAIRINQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAIRIPORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANDURI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARABA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARACAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARAPOAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIAPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARILIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARINOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARTINOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MENDONCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERIDIANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MESOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIGUELOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINEIROS DO TIETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRACATU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRA ESTRELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRANDOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRANTE DO PARANAPANEMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRASSOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRASSOLANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOCOCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOGI DAS CRUZES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOGI GUACU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOGI MIRIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOMBUCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONCOES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONGAGUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTE ALEGRE DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTE ALTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTE APRAZIVEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTE AZUL PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTE CASTELO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTEIRO LOBATO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTE MOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORRO AGUDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORUNGABA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOTUCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MURUTINGA DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NANTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NARANDIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NATIVIDADE DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAZARE PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEVES PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NHANDEARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIPOA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA ALIANCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA CAMPINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA CANAA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA CASTILHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA EUROPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA GRANADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA GUATAPORANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA LUZITANIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA ODESSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVO HORIZONTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUPORANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCAUCU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIMPIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONDA VERDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORIENTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORINDIUVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORLANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSASCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSCAR BRESSANE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSVALDO CRUZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OURINHOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUROESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OURO VERDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PACAEMBU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALESTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALMARES PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALMEIRA D'OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALMITAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANORAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARAGUACU PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARAIBUNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARAISO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARANAPANEMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARANAPUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARAPUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARDINHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARIQUERA-ACU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARISI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATROCINIO PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULICEIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULINIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULISTANIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO DE FARIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDERNEIRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRA BELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRANOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDREGULHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDREIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRINHAS PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO DE TOLEDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENAPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEREIRA BARRETO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEREIRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERUIBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIACATU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIEDADE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PILAR DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINDAMONHANGABA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINDORAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINHALZINHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIQUEROBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIQUETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRACAIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRACICABA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRAJU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRAJUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRANGI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRAPORA DO BOM JESUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRAPOZINHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRASSUNUNGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIRATININGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PITANGUEIRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLANALTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLATINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLONI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POMPEIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PONGAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PONTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PONTALINDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PONTES GESTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POPULINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORANGABA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTO FELIZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTO FERREIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POTIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POTIRENDABA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRACINHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRADOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRAIA GRANDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRATANIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRESIDENTE ALVES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRESIDENTE BERNARDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRESIDENTE EPITACIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRESIDENTE PRUDENTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRESIDENTE VENCESLAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROMISSAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUADRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUEIROZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUELUZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUINTANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RANCHARIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REDENCAO DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGENTE FEIJO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGINOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGISTRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESTINGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO BONITO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO BRANCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO CORRENTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO DOS INDIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO GRANDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO PIRES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBEIRAO PRETO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIVERSUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIFAINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RINCAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RINOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIO CLARO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIO DAS PEDRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIO GRANDE DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIOLANDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUBIACEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUBINEIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SABINO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAGRES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALES OLIVEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALESOPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALMOURAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALTINHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALTO DE PIRAPORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALTO GRANDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDOVALINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA ADELIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA ALBERTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA BARBARA D'OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA BRANCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA CLARA D'OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA CRUZ DA CONCEICAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA CRUZ DA ESPERANCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA CRUZ DAS PALMEIRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA CRUZ DO RIO PARDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA ERNESTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA FE DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA GERTRUDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA ISABEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA LUCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA MARIA DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA MERCEDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTANA DA PONTE PENSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTANA DE PARNAIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA RITA D'OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA RITA DO PASSA QUATRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA ROSA DE VITERBO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA SALETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO ANASTACIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO ANDRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO ANTONIO DA ALEGRIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO ANTONIO DE POSSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO ANTONIO DO ARACANGUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO ANTONIO DO JARDIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO ANTONIO DO PINHAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTO EXPEDITO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTOPOLIS DO AGUAPEI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO BENTO DO SAPUCAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO BERNARDO DO CAMPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO CAETANO DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO CARLOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO FRANCISCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOAO DA BOA VISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOAO DAS DUAS PONTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOAO DE IRACEMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOAO DO PAU D'ALHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOAQUIM DA BARRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOSE DA BELA VISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOSE DO BARREIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOSE DO RIO PARDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOSE DO RIO PRETO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO JOSE DOS CAMPOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO LOURENCO DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO LUIS DO PARAITINGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO MANUEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO MIGUEL ARCANJO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO PAULO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO PEDRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO PEDRO DO TURVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO ROQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO SEBASTIAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO SEBASTIAO DA GRAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO SIMAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAO VICENTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SARAPUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SARUTAIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEBASTIANOPOLIS DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERRA AZUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERRANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERRA NEGRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERTAOZINHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SETE BARRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEVERINIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILVEIRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOCORRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOROCABA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUD MENNUCCI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUZANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUZANAPOLIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABAPUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABATINGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABOAO DA SERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TACIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAGUAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIACU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIUVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TANABI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAPIRAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAPIRATIBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAQUARAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAQUARITINGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAQUARITUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAQUARIVAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TARABAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TARUMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TATUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAUBATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEJUPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEODORO SAMPAIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERRA ROXA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMBURI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TORRE DE PEDRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TORRINHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRABIJU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TREMEMBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRES FRONTEIRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUIUTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUPI PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TURIUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TURMALINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBARANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBATUBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBIRAJARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCHOA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIAO PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URANIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URUPES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALENTIM GENTIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALINHOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALPARAISO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARGEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARGEM GRANDE DO SUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARGEM GRANDE PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARZEA PAULISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERA CRUZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VINHEDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIRADOURO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VISTA ALEGRE DO ALTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITORIA BRASIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VOTORANTIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VOTUPORANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZACARIAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHAVANTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTIVA GERBI</t>
   </si>
 </sst>
 </file>
@@ -2057,7 +2048,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2184,21 +2175,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C648"/>
+  <dimension ref="A1:C646"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.76"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2206,7 +2197,7 @@
       <c r="A2" s="1" t="n">
         <v>350010</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="n">
@@ -2217,7 +2208,7 @@
       <c r="A3" s="1" t="n">
         <v>350020</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="2" t="n">
@@ -2228,7 +2219,7 @@
       <c r="A4" s="1" t="n">
         <v>350030</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="n">
@@ -2239,7 +2230,7 @@
       <c r="A5" s="1" t="n">
         <v>350040</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="n">
@@ -2250,7 +2241,7 @@
       <c r="A6" s="1" t="n">
         <v>350050</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="n">
@@ -2261,7 +2252,7 @@
       <c r="A7" s="1" t="n">
         <v>350055</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="2" t="n">
@@ -2272,7 +2263,7 @@
       <c r="A8" s="1" t="n">
         <v>350060</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="2" t="n">
@@ -2283,7 +2274,7 @@
       <c r="A9" s="1" t="n">
         <v>350070</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="2" t="n">
@@ -2294,7 +2285,7 @@
       <c r="A10" s="1" t="n">
         <v>350075</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="2" t="n">
@@ -2305,7 +2296,7 @@
       <c r="A11" s="1" t="n">
         <v>350080</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="2" t="n">
@@ -2316,7 +2307,7 @@
       <c r="A12" s="1" t="n">
         <v>350090</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="2" t="n">
@@ -2327,7 +2318,7 @@
       <c r="A13" s="1" t="n">
         <v>350100</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="2" t="n">
@@ -2338,7 +2329,7 @@
       <c r="A14" s="1" t="n">
         <v>350110</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="2" t="n">
@@ -2349,7 +2340,7 @@
       <c r="A15" s="1" t="n">
         <v>350115</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="2" t="n">
@@ -2360,7 +2351,7 @@
       <c r="A16" s="1" t="n">
         <v>350120</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="2" t="n">
@@ -2371,7 +2362,7 @@
       <c r="A17" s="1" t="n">
         <v>350130</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="2" t="n">
@@ -2382,7 +2373,7 @@
       <c r="A18" s="1" t="n">
         <v>350140</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="2" t="n">
@@ -2393,7 +2384,7 @@
       <c r="A19" s="1" t="n">
         <v>350150</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="2" t="n">
@@ -2404,7 +2395,7 @@
       <c r="A20" s="1" t="n">
         <v>350160</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="2" t="n">
@@ -2415,7 +2406,7 @@
       <c r="A21" s="1" t="n">
         <v>350170</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="2" t="n">
@@ -2426,7 +2417,7 @@
       <c r="A22" s="1" t="n">
         <v>350180</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="2" t="n">
@@ -2437,7 +2428,7 @@
       <c r="A23" s="1" t="n">
         <v>350190</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="2" t="n">
@@ -2448,7 +2439,7 @@
       <c r="A24" s="1" t="n">
         <v>350200</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C24" s="2" t="n">
@@ -2459,7 +2450,7 @@
       <c r="A25" s="1" t="n">
         <v>350210</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="2" t="n">
@@ -2470,7 +2461,7 @@
       <c r="A26" s="1" t="n">
         <v>350220</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="2" t="n">
@@ -2481,7 +2472,7 @@
       <c r="A27" s="1" t="n">
         <v>350230</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C27" s="2" t="n">
@@ -2492,7 +2483,7 @@
       <c r="A28" s="1" t="n">
         <v>350240</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="2" t="n">
@@ -2503,7 +2494,7 @@
       <c r="A29" s="1" t="n">
         <v>350250</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C29" s="2" t="n">
@@ -2514,7 +2505,7 @@
       <c r="A30" s="1" t="n">
         <v>350260</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="2" t="n">
@@ -2525,7 +2516,7 @@
       <c r="A31" s="1" t="n">
         <v>350270</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C31" s="2" t="n">
@@ -2536,7 +2527,7 @@
       <c r="A32" s="1" t="n">
         <v>350275</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C32" s="2" t="n">
@@ -2547,7 +2538,7 @@
       <c r="A33" s="1" t="n">
         <v>350280</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C33" s="2" t="n">
@@ -2558,7 +2549,7 @@
       <c r="A34" s="1" t="n">
         <v>350290</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C34" s="2" t="n">
@@ -2569,7 +2560,7 @@
       <c r="A35" s="1" t="n">
         <v>350300</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C35" s="2" t="n">
@@ -2580,7 +2571,7 @@
       <c r="A36" s="1" t="n">
         <v>350310</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C36" s="2" t="n">
@@ -2591,7 +2582,7 @@
       <c r="A37" s="1" t="n">
         <v>350315</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C37" s="2" t="n">
@@ -2602,7 +2593,7 @@
       <c r="A38" s="1" t="n">
         <v>350320</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C38" s="2" t="n">
@@ -2613,7 +2604,7 @@
       <c r="A39" s="1" t="n">
         <v>350330</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C39" s="2" t="n">
@@ -2624,7 +2615,7 @@
       <c r="A40" s="1" t="n">
         <v>350335</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C40" s="2" t="n">
@@ -2635,7 +2626,7 @@
       <c r="A41" s="1" t="n">
         <v>350340</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C41" s="2" t="n">
@@ -2646,7 +2637,7 @@
       <c r="A42" s="1" t="n">
         <v>350350</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="2" t="n">
@@ -2657,7 +2648,7 @@
       <c r="A43" s="1" t="n">
         <v>350360</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C43" s="2" t="n">
@@ -2668,7 +2659,7 @@
       <c r="A44" s="1" t="n">
         <v>350370</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C44" s="2" t="n">
@@ -2679,7 +2670,7 @@
       <c r="A45" s="1" t="n">
         <v>350380</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C45" s="2" t="n">
@@ -2690,7 +2681,7 @@
       <c r="A46" s="1" t="n">
         <v>350390</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C46" s="2" t="n">
@@ -2701,7 +2692,7 @@
       <c r="A47" s="1" t="n">
         <v>350395</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C47" s="2" t="n">
@@ -2712,7 +2703,7 @@
       <c r="A48" s="1" t="n">
         <v>350400</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C48" s="2" t="n">
@@ -2723,7 +2714,7 @@
       <c r="A49" s="1" t="n">
         <v>350410</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C49" s="2" t="n">
@@ -2734,7 +2725,7 @@
       <c r="A50" s="1" t="n">
         <v>350420</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C50" s="2" t="n">
@@ -2745,7 +2736,7 @@
       <c r="A51" s="1" t="n">
         <v>350430</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C51" s="2" t="n">
@@ -2756,7 +2747,7 @@
       <c r="A52" s="1" t="n">
         <v>350440</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C52" s="2" t="n">
@@ -2767,7 +2758,7 @@
       <c r="A53" s="1" t="n">
         <v>350450</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C53" s="2" t="n">
@@ -2778,7 +2769,7 @@
       <c r="A54" s="1" t="n">
         <v>350460</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C54" s="2" t="n">
@@ -2789,7 +2780,7 @@
       <c r="A55" s="1" t="n">
         <v>350470</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C55" s="2" t="n">
@@ -2800,7 +2791,7 @@
       <c r="A56" s="1" t="n">
         <v>350480</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="B56" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C56" s="2" t="n">
@@ -2811,7 +2802,7 @@
       <c r="A57" s="1" t="n">
         <v>350490</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C57" s="2" t="n">
@@ -2822,7 +2813,7 @@
       <c r="A58" s="1" t="n">
         <v>350500</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C58" s="2" t="n">
@@ -2833,7 +2824,7 @@
       <c r="A59" s="1" t="n">
         <v>350510</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C59" s="2" t="n">
@@ -2844,7 +2835,7 @@
       <c r="A60" s="1" t="n">
         <v>350520</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C60" s="2" t="n">
@@ -2855,7 +2846,7 @@
       <c r="A61" s="1" t="n">
         <v>350530</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C61" s="2" t="n">
@@ -2866,7 +2857,7 @@
       <c r="A62" s="1" t="n">
         <v>350535</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C62" s="2" t="n">
@@ -2877,7 +2868,7 @@
       <c r="A63" s="1" t="n">
         <v>350540</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C63" s="2" t="n">
@@ -2888,7 +2879,7 @@
       <c r="A64" s="1" t="n">
         <v>350550</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="B64" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C64" s="2" t="n">
@@ -2899,7 +2890,7 @@
       <c r="A65" s="1" t="n">
         <v>350560</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="B65" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C65" s="2" t="n">
@@ -2910,7 +2901,7 @@
       <c r="A66" s="1" t="n">
         <v>350570</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C66" s="2" t="n">
@@ -2921,7 +2912,7 @@
       <c r="A67" s="1" t="n">
         <v>350580</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C67" s="2" t="n">
@@ -2932,7 +2923,7 @@
       <c r="A68" s="1" t="n">
         <v>350590</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C68" s="2" t="n">
@@ -2943,7 +2934,7 @@
       <c r="A69" s="1" t="n">
         <v>350600</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C69" s="2" t="n">
@@ -2954,7 +2945,7 @@
       <c r="A70" s="1" t="n">
         <v>350610</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C70" s="2" t="n">
@@ -2965,7 +2956,7 @@
       <c r="A71" s="1" t="n">
         <v>350620</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C71" s="2" t="n">
@@ -2976,7 +2967,7 @@
       <c r="A72" s="1" t="n">
         <v>350630</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="B72" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C72" s="2" t="n">
@@ -2987,7 +2978,7 @@
       <c r="A73" s="1" t="n">
         <v>350635</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="B73" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C73" s="2" t="n">
@@ -2998,7 +2989,7 @@
       <c r="A74" s="1" t="n">
         <v>350640</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="B74" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C74" s="2" t="n">
@@ -3009,7 +3000,7 @@
       <c r="A75" s="1" t="n">
         <v>350650</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="B75" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C75" s="2" t="n">
@@ -3020,7 +3011,7 @@
       <c r="A76" s="1" t="n">
         <v>350660</v>
       </c>
-      <c r="B76" s="0" t="s">
+      <c r="B76" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C76" s="2" t="n">
@@ -3031,7 +3022,7 @@
       <c r="A77" s="1" t="n">
         <v>350670</v>
       </c>
-      <c r="B77" s="0" t="s">
+      <c r="B77" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C77" s="2" t="n">
@@ -3042,7 +3033,7 @@
       <c r="A78" s="1" t="n">
         <v>350680</v>
       </c>
-      <c r="B78" s="0" t="s">
+      <c r="B78" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C78" s="2" t="n">
@@ -3053,7 +3044,7 @@
       <c r="A79" s="1" t="n">
         <v>350690</v>
       </c>
-      <c r="B79" s="0" t="s">
+      <c r="B79" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C79" s="2" t="n">
@@ -3064,7 +3055,7 @@
       <c r="A80" s="1" t="n">
         <v>350700</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="B80" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C80" s="2" t="n">
@@ -3075,7 +3066,7 @@
       <c r="A81" s="1" t="n">
         <v>350710</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="B81" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C81" s="2" t="n">
@@ -3086,7 +3077,7 @@
       <c r="A82" s="1" t="n">
         <v>350715</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="B82" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C82" s="2" t="n">
@@ -3097,7 +3088,7 @@
       <c r="A83" s="1" t="n">
         <v>350720</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="B83" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C83" s="2" t="n">
@@ -3108,7 +3099,7 @@
       <c r="A84" s="1" t="n">
         <v>350730</v>
       </c>
-      <c r="B84" s="0" t="s">
+      <c r="B84" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C84" s="2" t="n">
@@ -3119,7 +3110,7 @@
       <c r="A85" s="1" t="n">
         <v>350740</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="B85" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C85" s="2" t="n">
@@ -3130,7 +3121,7 @@
       <c r="A86" s="1" t="n">
         <v>350745</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="B86" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C86" s="2" t="n">
@@ -3141,7 +3132,7 @@
       <c r="A87" s="1" t="n">
         <v>350750</v>
       </c>
-      <c r="B87" s="0" t="s">
+      <c r="B87" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C87" s="2" t="n">
@@ -3152,7 +3143,7 @@
       <c r="A88" s="1" t="n">
         <v>350760</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="B88" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C88" s="2" t="n">
@@ -3163,7 +3154,7 @@
       <c r="A89" s="1" t="n">
         <v>350770</v>
       </c>
-      <c r="B89" s="0" t="s">
+      <c r="B89" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C89" s="2" t="n">
@@ -3174,7 +3165,7 @@
       <c r="A90" s="1" t="n">
         <v>350775</v>
       </c>
-      <c r="B90" s="0" t="s">
+      <c r="B90" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C90" s="2" t="n">
@@ -3185,7 +3176,7 @@
       <c r="A91" s="1" t="n">
         <v>350780</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="B91" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C91" s="2" t="n">
@@ -3196,7 +3187,7 @@
       <c r="A92" s="1" t="n">
         <v>350790</v>
       </c>
-      <c r="B92" s="0" t="s">
+      <c r="B92" s="1" t="s">
         <v>93</v>
       </c>
       <c r="C92" s="2" t="n">
@@ -3207,7 +3198,7 @@
       <c r="A93" s="1" t="n">
         <v>350800</v>
       </c>
-      <c r="B93" s="0" t="s">
+      <c r="B93" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C93" s="2" t="n">
@@ -3218,7 +3209,7 @@
       <c r="A94" s="1" t="n">
         <v>350810</v>
       </c>
-      <c r="B94" s="0" t="s">
+      <c r="B94" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C94" s="2" t="n">
@@ -3229,7 +3220,7 @@
       <c r="A95" s="1" t="n">
         <v>350820</v>
       </c>
-      <c r="B95" s="0" t="s">
+      <c r="B95" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C95" s="2" t="n">
@@ -3240,7 +3231,7 @@
       <c r="A96" s="1" t="n">
         <v>350830</v>
       </c>
-      <c r="B96" s="0" t="s">
+      <c r="B96" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C96" s="2" t="n">
@@ -3251,7 +3242,7 @@
       <c r="A97" s="1" t="n">
         <v>350840</v>
       </c>
-      <c r="B97" s="0" t="s">
+      <c r="B97" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C97" s="2" t="n">
@@ -3262,7 +3253,7 @@
       <c r="A98" s="1" t="n">
         <v>350850</v>
       </c>
-      <c r="B98" s="0" t="s">
+      <c r="B98" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C98" s="2" t="n">
@@ -3273,7 +3264,7 @@
       <c r="A99" s="1" t="n">
         <v>350860</v>
       </c>
-      <c r="B99" s="0" t="s">
+      <c r="B99" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C99" s="2" t="n">
@@ -3284,7 +3275,7 @@
       <c r="A100" s="1" t="n">
         <v>350870</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="B100" s="1" t="s">
         <v>101</v>
       </c>
       <c r="C100" s="2" t="n">
@@ -3295,7 +3286,7 @@
       <c r="A101" s="1" t="n">
         <v>350880</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="B101" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C101" s="2" t="n">
@@ -3306,7 +3297,7 @@
       <c r="A102" s="1" t="n">
         <v>350890</v>
       </c>
-      <c r="B102" s="0" t="s">
+      <c r="B102" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C102" s="2" t="n">
@@ -3317,7 +3308,7 @@
       <c r="A103" s="1" t="n">
         <v>350900</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="B103" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C103" s="2" t="n">
@@ -3328,7 +3319,7 @@
       <c r="A104" s="1" t="n">
         <v>350910</v>
       </c>
-      <c r="B104" s="0" t="s">
+      <c r="B104" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C104" s="2" t="n">
@@ -3339,7 +3330,7 @@
       <c r="A105" s="1" t="n">
         <v>350920</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="B105" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C105" s="2" t="n">
@@ -3350,7 +3341,7 @@
       <c r="A106" s="1" t="n">
         <v>350925</v>
       </c>
-      <c r="B106" s="0" t="s">
+      <c r="B106" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C106" s="2" t="n">
@@ -3361,7 +3352,7 @@
       <c r="A107" s="1" t="n">
         <v>350930</v>
       </c>
-      <c r="B107" s="0" t="s">
+      <c r="B107" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C107" s="2" t="n">
@@ -3372,7 +3363,7 @@
       <c r="A108" s="1" t="n">
         <v>350940</v>
       </c>
-      <c r="B108" s="0" t="s">
+      <c r="B108" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C108" s="2" t="n">
@@ -3383,7 +3374,7 @@
       <c r="A109" s="1" t="n">
         <v>350945</v>
       </c>
-      <c r="B109" s="0" t="s">
+      <c r="B109" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C109" s="2" t="n">
@@ -3394,7 +3385,7 @@
       <c r="A110" s="1" t="n">
         <v>350950</v>
       </c>
-      <c r="B110" s="0" t="s">
+      <c r="B110" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C110" s="2" t="n">
@@ -3405,7 +3396,7 @@
       <c r="A111" s="1" t="n">
         <v>350960</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="B111" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C111" s="2" t="n">
@@ -3416,7 +3407,7 @@
       <c r="A112" s="1" t="n">
         <v>350970</v>
       </c>
-      <c r="B112" s="0" t="s">
+      <c r="B112" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C112" s="2" t="n">
@@ -3427,7 +3418,7 @@
       <c r="A113" s="1" t="n">
         <v>350980</v>
       </c>
-      <c r="B113" s="0" t="s">
+      <c r="B113" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C113" s="2" t="n">
@@ -3438,7 +3429,7 @@
       <c r="A114" s="1" t="n">
         <v>350990</v>
       </c>
-      <c r="B114" s="0" t="s">
+      <c r="B114" s="1" t="s">
         <v>115</v>
       </c>
       <c r="C114" s="2" t="n">
@@ -3449,7 +3440,7 @@
       <c r="A115" s="1" t="n">
         <v>350995</v>
       </c>
-      <c r="B115" s="0" t="s">
+      <c r="B115" s="1" t="s">
         <v>116</v>
       </c>
       <c r="C115" s="2" t="n">
@@ -3460,7 +3451,7 @@
       <c r="A116" s="1" t="n">
         <v>351000</v>
       </c>
-      <c r="B116" s="0" t="s">
+      <c r="B116" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C116" s="2" t="n">
@@ -3471,7 +3462,7 @@
       <c r="A117" s="1" t="n">
         <v>351010</v>
       </c>
-      <c r="B117" s="0" t="s">
+      <c r="B117" s="1" t="s">
         <v>118</v>
       </c>
       <c r="C117" s="2" t="n">
@@ -3482,7 +3473,7 @@
       <c r="A118" s="1" t="n">
         <v>351015</v>
       </c>
-      <c r="B118" s="0" t="s">
+      <c r="B118" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C118" s="2" t="n">
@@ -3493,7 +3484,7 @@
       <c r="A119" s="1" t="n">
         <v>351020</v>
       </c>
-      <c r="B119" s="0" t="s">
+      <c r="B119" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C119" s="2" t="n">
@@ -3504,7 +3495,7 @@
       <c r="A120" s="1" t="n">
         <v>351030</v>
       </c>
-      <c r="B120" s="0" t="s">
+      <c r="B120" s="1" t="s">
         <v>121</v>
       </c>
       <c r="C120" s="2" t="n">
@@ -3515,7 +3506,7 @@
       <c r="A121" s="1" t="n">
         <v>351040</v>
       </c>
-      <c r="B121" s="0" t="s">
+      <c r="B121" s="1" t="s">
         <v>122</v>
       </c>
       <c r="C121" s="2" t="n">
@@ -3526,7 +3517,7 @@
       <c r="A122" s="1" t="n">
         <v>351050</v>
       </c>
-      <c r="B122" s="0" t="s">
+      <c r="B122" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C122" s="2" t="n">
@@ -3537,7 +3528,7 @@
       <c r="A123" s="1" t="n">
         <v>351060</v>
       </c>
-      <c r="B123" s="0" t="s">
+      <c r="B123" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C123" s="2" t="n">
@@ -3548,7 +3539,7 @@
       <c r="A124" s="1" t="n">
         <v>351070</v>
       </c>
-      <c r="B124" s="0" t="s">
+      <c r="B124" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C124" s="2" t="n">
@@ -3559,7 +3550,7 @@
       <c r="A125" s="1" t="n">
         <v>351080</v>
       </c>
-      <c r="B125" s="0" t="s">
+      <c r="B125" s="1" t="s">
         <v>126</v>
       </c>
       <c r="C125" s="2" t="n">
@@ -3570,7 +3561,7 @@
       <c r="A126" s="1" t="n">
         <v>351090</v>
       </c>
-      <c r="B126" s="0" t="s">
+      <c r="B126" s="1" t="s">
         <v>127</v>
       </c>
       <c r="C126" s="2" t="n">
@@ -3581,7 +3572,7 @@
       <c r="A127" s="1" t="n">
         <v>351100</v>
       </c>
-      <c r="B127" s="0" t="s">
+      <c r="B127" s="1" t="s">
         <v>128</v>
       </c>
       <c r="C127" s="2" t="n">
@@ -3592,7 +3583,7 @@
       <c r="A128" s="1" t="n">
         <v>351110</v>
       </c>
-      <c r="B128" s="0" t="s">
+      <c r="B128" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C128" s="2" t="n">
@@ -3603,7 +3594,7 @@
       <c r="A129" s="1" t="n">
         <v>351120</v>
       </c>
-      <c r="B129" s="0" t="s">
+      <c r="B129" s="1" t="s">
         <v>130</v>
       </c>
       <c r="C129" s="2" t="n">
@@ -3614,7 +3605,7 @@
       <c r="A130" s="1" t="n">
         <v>351130</v>
       </c>
-      <c r="B130" s="0" t="s">
+      <c r="B130" s="1" t="s">
         <v>131</v>
       </c>
       <c r="C130" s="2" t="n">
@@ -3625,7 +3616,7 @@
       <c r="A131" s="1" t="n">
         <v>351140</v>
       </c>
-      <c r="B131" s="0" t="s">
+      <c r="B131" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C131" s="2" t="n">
@@ -3636,7 +3627,7 @@
       <c r="A132" s="1" t="n">
         <v>351150</v>
       </c>
-      <c r="B132" s="0" t="s">
+      <c r="B132" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C132" s="2" t="n">
@@ -3647,7 +3638,7 @@
       <c r="A133" s="1" t="n">
         <v>351160</v>
       </c>
-      <c r="B133" s="0" t="s">
+      <c r="B133" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C133" s="2" t="n">
@@ -3658,7 +3649,7 @@
       <c r="A134" s="1" t="n">
         <v>351170</v>
       </c>
-      <c r="B134" s="0" t="s">
+      <c r="B134" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C134" s="2" t="n">
@@ -3669,7 +3660,7 @@
       <c r="A135" s="1" t="n">
         <v>351190</v>
       </c>
-      <c r="B135" s="0" t="s">
+      <c r="B135" s="1" t="s">
         <v>136</v>
       </c>
       <c r="C135" s="2" t="n">
@@ -3680,7 +3671,7 @@
       <c r="A136" s="1" t="n">
         <v>351200</v>
       </c>
-      <c r="B136" s="0" t="s">
+      <c r="B136" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C136" s="2" t="n">
@@ -3691,7 +3682,7 @@
       <c r="A137" s="1" t="n">
         <v>351210</v>
       </c>
-      <c r="B137" s="0" t="s">
+      <c r="B137" s="1" t="s">
         <v>138</v>
       </c>
       <c r="C137" s="2" t="n">
@@ -3702,7 +3693,7 @@
       <c r="A138" s="1" t="n">
         <v>351220</v>
       </c>
-      <c r="B138" s="0" t="s">
+      <c r="B138" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C138" s="2" t="n">
@@ -3713,7 +3704,7 @@
       <c r="A139" s="1" t="n">
         <v>351230</v>
       </c>
-      <c r="B139" s="0" t="s">
+      <c r="B139" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C139" s="2" t="n">
@@ -3724,7 +3715,7 @@
       <c r="A140" s="1" t="n">
         <v>351240</v>
       </c>
-      <c r="B140" s="0" t="s">
+      <c r="B140" s="1" t="s">
         <v>141</v>
       </c>
       <c r="C140" s="2" t="n">
@@ -3735,7 +3726,7 @@
       <c r="A141" s="1" t="n">
         <v>351250</v>
       </c>
-      <c r="B141" s="0" t="s">
+      <c r="B141" s="1" t="s">
         <v>142</v>
       </c>
       <c r="C141" s="2" t="n">
@@ -3746,7 +3737,7 @@
       <c r="A142" s="1" t="n">
         <v>351260</v>
       </c>
-      <c r="B142" s="0" t="s">
+      <c r="B142" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C142" s="2" t="n">
@@ -3757,7 +3748,7 @@
       <c r="A143" s="1" t="n">
         <v>351270</v>
       </c>
-      <c r="B143" s="0" t="s">
+      <c r="B143" s="1" t="s">
         <v>144</v>
       </c>
       <c r="C143" s="2" t="n">
@@ -3768,7 +3759,7 @@
       <c r="A144" s="1" t="n">
         <v>351280</v>
       </c>
-      <c r="B144" s="0" t="s">
+      <c r="B144" s="1" t="s">
         <v>145</v>
       </c>
       <c r="C144" s="2" t="n">
@@ -3779,7 +3770,7 @@
       <c r="A145" s="1" t="n">
         <v>351290</v>
       </c>
-      <c r="B145" s="0" t="s">
+      <c r="B145" s="1" t="s">
         <v>146</v>
       </c>
       <c r="C145" s="2" t="n">
@@ -3790,7 +3781,7 @@
       <c r="A146" s="1" t="n">
         <v>351300</v>
       </c>
-      <c r="B146" s="0" t="s">
+      <c r="B146" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C146" s="2" t="n">
@@ -3801,7 +3792,7 @@
       <c r="A147" s="1" t="n">
         <v>351310</v>
       </c>
-      <c r="B147" s="0" t="s">
+      <c r="B147" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C147" s="2" t="n">
@@ -3812,7 +3803,7 @@
       <c r="A148" s="1" t="n">
         <v>351320</v>
       </c>
-      <c r="B148" s="0" t="s">
+      <c r="B148" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C148" s="2" t="n">
@@ -3823,7 +3814,7 @@
       <c r="A149" s="1" t="n">
         <v>351330</v>
       </c>
-      <c r="B149" s="0" t="s">
+      <c r="B149" s="1" t="s">
         <v>150</v>
       </c>
       <c r="C149" s="2" t="n">
@@ -3834,7 +3825,7 @@
       <c r="A150" s="1" t="n">
         <v>351340</v>
       </c>
-      <c r="B150" s="0" t="s">
+      <c r="B150" s="1" t="s">
         <v>151</v>
       </c>
       <c r="C150" s="2" t="n">
@@ -3845,7 +3836,7 @@
       <c r="A151" s="1" t="n">
         <v>351350</v>
       </c>
-      <c r="B151" s="0" t="s">
+      <c r="B151" s="1" t="s">
         <v>152</v>
       </c>
       <c r="C151" s="2" t="n">
@@ -3856,7 +3847,7 @@
       <c r="A152" s="1" t="n">
         <v>351360</v>
       </c>
-      <c r="B152" s="0" t="s">
+      <c r="B152" s="1" t="s">
         <v>153</v>
       </c>
       <c r="C152" s="2" t="n">
@@ -3867,7 +3858,7 @@
       <c r="A153" s="1" t="n">
         <v>351370</v>
       </c>
-      <c r="B153" s="0" t="s">
+      <c r="B153" s="1" t="s">
         <v>154</v>
       </c>
       <c r="C153" s="2" t="n">
@@ -3878,7 +3869,7 @@
       <c r="A154" s="1" t="n">
         <v>351380</v>
       </c>
-      <c r="B154" s="0" t="s">
+      <c r="B154" s="1" t="s">
         <v>155</v>
       </c>
       <c r="C154" s="2" t="n">
@@ -3889,7 +3880,7 @@
       <c r="A155" s="1" t="n">
         <v>351385</v>
       </c>
-      <c r="B155" s="0" t="s">
+      <c r="B155" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C155" s="2" t="n">
@@ -3900,7 +3891,7 @@
       <c r="A156" s="1" t="n">
         <v>351390</v>
       </c>
-      <c r="B156" s="0" t="s">
+      <c r="B156" s="1" t="s">
         <v>157</v>
       </c>
       <c r="C156" s="2" t="n">
@@ -3911,7 +3902,7 @@
       <c r="A157" s="1" t="n">
         <v>351400</v>
       </c>
-      <c r="B157" s="0" t="s">
+      <c r="B157" s="1" t="s">
         <v>158</v>
       </c>
       <c r="C157" s="2" t="n">
@@ -3922,7 +3913,7 @@
       <c r="A158" s="1" t="n">
         <v>351410</v>
       </c>
-      <c r="B158" s="0" t="s">
+      <c r="B158" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C158" s="2" t="n">
@@ -3933,7 +3924,7 @@
       <c r="A159" s="1" t="n">
         <v>351420</v>
       </c>
-      <c r="B159" s="0" t="s">
+      <c r="B159" s="1" t="s">
         <v>160</v>
       </c>
       <c r="C159" s="2" t="n">
@@ -3944,7 +3935,7 @@
       <c r="A160" s="1" t="n">
         <v>351430</v>
       </c>
-      <c r="B160" s="0" t="s">
+      <c r="B160" s="1" t="s">
         <v>161</v>
       </c>
       <c r="C160" s="2" t="n">
@@ -3955,7 +3946,7 @@
       <c r="A161" s="1" t="n">
         <v>351440</v>
       </c>
-      <c r="B161" s="0" t="s">
+      <c r="B161" s="1" t="s">
         <v>162</v>
       </c>
       <c r="C161" s="2" t="n">
@@ -3966,7 +3957,7 @@
       <c r="A162" s="1" t="n">
         <v>351450</v>
       </c>
-      <c r="B162" s="0" t="s">
+      <c r="B162" s="1" t="s">
         <v>163</v>
       </c>
       <c r="C162" s="2" t="n">
@@ -3977,7 +3968,7 @@
       <c r="A163" s="1" t="n">
         <v>351460</v>
       </c>
-      <c r="B163" s="0" t="s">
+      <c r="B163" s="1" t="s">
         <v>164</v>
       </c>
       <c r="C163" s="2" t="n">
@@ -3988,7 +3979,7 @@
       <c r="A164" s="1" t="n">
         <v>351470</v>
       </c>
-      <c r="B164" s="0" t="s">
+      <c r="B164" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C164" s="2" t="n">
@@ -3999,7 +3990,7 @@
       <c r="A165" s="1" t="n">
         <v>351480</v>
       </c>
-      <c r="B165" s="0" t="s">
+      <c r="B165" s="1" t="s">
         <v>166</v>
       </c>
       <c r="C165" s="2" t="n">
@@ -4010,7 +4001,7 @@
       <c r="A166" s="1" t="n">
         <v>351490</v>
       </c>
-      <c r="B166" s="0" t="s">
+      <c r="B166" s="1" t="s">
         <v>167</v>
       </c>
       <c r="C166" s="2" t="n">
@@ -4021,7 +4012,7 @@
       <c r="A167" s="1" t="n">
         <v>351492</v>
       </c>
-      <c r="B167" s="0" t="s">
+      <c r="B167" s="1" t="s">
         <v>168</v>
       </c>
       <c r="C167" s="2" t="n">
@@ -4032,7 +4023,7 @@
       <c r="A168" s="1" t="n">
         <v>351495</v>
       </c>
-      <c r="B168" s="0" t="s">
+      <c r="B168" s="1" t="s">
         <v>169</v>
       </c>
       <c r="C168" s="2" t="n">
@@ -4043,7 +4034,7 @@
       <c r="A169" s="1" t="n">
         <v>351500</v>
       </c>
-      <c r="B169" s="0" t="s">
+      <c r="B169" s="1" t="s">
         <v>170</v>
       </c>
       <c r="C169" s="2" t="n">
@@ -4054,7 +4045,7 @@
       <c r="A170" s="1" t="n">
         <v>351510</v>
       </c>
-      <c r="B170" s="0" t="s">
+      <c r="B170" s="1" t="s">
         <v>171</v>
       </c>
       <c r="C170" s="2" t="n">
@@ -4065,7 +4056,7 @@
       <c r="A171" s="1" t="n">
         <v>351512</v>
       </c>
-      <c r="B171" s="0" t="s">
+      <c r="B171" s="1" t="s">
         <v>172</v>
       </c>
       <c r="C171" s="2" t="n">
@@ -4076,7 +4067,7 @@
       <c r="A172" s="1" t="n">
         <v>351515</v>
       </c>
-      <c r="B172" s="0" t="s">
+      <c r="B172" s="1" t="s">
         <v>173</v>
       </c>
       <c r="C172" s="2" t="n">
@@ -4087,7 +4078,7 @@
       <c r="A173" s="1" t="n">
         <v>351518</v>
       </c>
-      <c r="B173" s="0" t="s">
+      <c r="B173" s="1" t="s">
         <v>174</v>
       </c>
       <c r="C173" s="2" t="n">
@@ -4098,7 +4089,7 @@
       <c r="A174" s="1" t="n">
         <v>351519</v>
       </c>
-      <c r="B174" s="0" t="s">
+      <c r="B174" s="1" t="s">
         <v>175</v>
       </c>
       <c r="C174" s="2" t="n">
@@ -4109,7 +4100,7 @@
       <c r="A175" s="1" t="n">
         <v>351520</v>
       </c>
-      <c r="B175" s="0" t="s">
+      <c r="B175" s="1" t="s">
         <v>176</v>
       </c>
       <c r="C175" s="2" t="n">
@@ -4120,7 +4111,7 @@
       <c r="A176" s="1" t="n">
         <v>351530</v>
       </c>
-      <c r="B176" s="0" t="s">
+      <c r="B176" s="1" t="s">
         <v>177</v>
       </c>
       <c r="C176" s="2" t="n">
@@ -4131,7 +4122,7 @@
       <c r="A177" s="1" t="n">
         <v>351535</v>
       </c>
-      <c r="B177" s="0" t="s">
+      <c r="B177" s="1" t="s">
         <v>178</v>
       </c>
       <c r="C177" s="2" t="n">
@@ -4142,7 +4133,7 @@
       <c r="A178" s="1" t="n">
         <v>351540</v>
       </c>
-      <c r="B178" s="0" t="s">
+      <c r="B178" s="1" t="s">
         <v>179</v>
       </c>
       <c r="C178" s="2" t="n">
@@ -4153,7 +4144,7 @@
       <c r="A179" s="1" t="n">
         <v>351550</v>
       </c>
-      <c r="B179" s="0" t="s">
+      <c r="B179" s="1" t="s">
         <v>180</v>
       </c>
       <c r="C179" s="2" t="n">
@@ -4164,7 +4155,7 @@
       <c r="A180" s="1" t="n">
         <v>351560</v>
       </c>
-      <c r="B180" s="0" t="s">
+      <c r="B180" s="1" t="s">
         <v>181</v>
       </c>
       <c r="C180" s="2" t="n">
@@ -4175,7 +4166,7 @@
       <c r="A181" s="1" t="n">
         <v>351565</v>
       </c>
-      <c r="B181" s="0" t="s">
+      <c r="B181" s="1" t="s">
         <v>182</v>
       </c>
       <c r="C181" s="2" t="n">
@@ -4186,7 +4177,7 @@
       <c r="A182" s="1" t="n">
         <v>351570</v>
       </c>
-      <c r="B182" s="0" t="s">
+      <c r="B182" s="1" t="s">
         <v>183</v>
       </c>
       <c r="C182" s="2" t="n">
@@ -4197,7 +4188,7 @@
       <c r="A183" s="1" t="n">
         <v>351580</v>
       </c>
-      <c r="B183" s="0" t="s">
+      <c r="B183" s="1" t="s">
         <v>184</v>
       </c>
       <c r="C183" s="2" t="n">
@@ -4208,7 +4199,7 @@
       <c r="A184" s="1" t="n">
         <v>351590</v>
       </c>
-      <c r="B184" s="0" t="s">
+      <c r="B184" s="1" t="s">
         <v>185</v>
       </c>
       <c r="C184" s="2" t="n">
@@ -4219,7 +4210,7 @@
       <c r="A185" s="1" t="n">
         <v>351600</v>
       </c>
-      <c r="B185" s="0" t="s">
+      <c r="B185" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C185" s="2" t="n">
@@ -4230,7 +4221,7 @@
       <c r="A186" s="1" t="n">
         <v>351610</v>
       </c>
-      <c r="B186" s="0" t="s">
+      <c r="B186" s="1" t="s">
         <v>187</v>
       </c>
       <c r="C186" s="2" t="n">
@@ -4241,7 +4232,7 @@
       <c r="A187" s="1" t="n">
         <v>351620</v>
       </c>
-      <c r="B187" s="0" t="s">
+      <c r="B187" s="1" t="s">
         <v>188</v>
       </c>
       <c r="C187" s="2" t="n">
@@ -4252,7 +4243,7 @@
       <c r="A188" s="1" t="n">
         <v>351630</v>
       </c>
-      <c r="B188" s="0" t="s">
+      <c r="B188" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C188" s="2" t="n">
@@ -4263,7 +4254,7 @@
       <c r="A189" s="1" t="n">
         <v>351640</v>
       </c>
-      <c r="B189" s="0" t="s">
+      <c r="B189" s="1" t="s">
         <v>190</v>
       </c>
       <c r="C189" s="2" t="n">
@@ -4274,7 +4265,7 @@
       <c r="A190" s="1" t="n">
         <v>351650</v>
       </c>
-      <c r="B190" s="0" t="s">
+      <c r="B190" s="1" t="s">
         <v>191</v>
       </c>
       <c r="C190" s="2" t="n">
@@ -4285,7 +4276,7 @@
       <c r="A191" s="1" t="n">
         <v>351660</v>
       </c>
-      <c r="B191" s="0" t="s">
+      <c r="B191" s="1" t="s">
         <v>192</v>
       </c>
       <c r="C191" s="2" t="n">
@@ -4296,7 +4287,7 @@
       <c r="A192" s="1" t="n">
         <v>351670</v>
       </c>
-      <c r="B192" s="0" t="s">
+      <c r="B192" s="1" t="s">
         <v>193</v>
       </c>
       <c r="C192" s="2" t="n">
@@ -4307,7 +4298,7 @@
       <c r="A193" s="1" t="n">
         <v>351680</v>
       </c>
-      <c r="B193" s="0" t="s">
+      <c r="B193" s="1" t="s">
         <v>194</v>
       </c>
       <c r="C193" s="2" t="n">
@@ -4318,7 +4309,7 @@
       <c r="A194" s="1" t="n">
         <v>351685</v>
       </c>
-      <c r="B194" s="0" t="s">
+      <c r="B194" s="1" t="s">
         <v>195</v>
       </c>
       <c r="C194" s="2" t="n">
@@ -4329,7 +4320,7 @@
       <c r="A195" s="1" t="n">
         <v>351690</v>
       </c>
-      <c r="B195" s="0" t="s">
+      <c r="B195" s="1" t="s">
         <v>196</v>
       </c>
       <c r="C195" s="2" t="n">
@@ -4340,7 +4331,7 @@
       <c r="A196" s="1" t="n">
         <v>351700</v>
       </c>
-      <c r="B196" s="0" t="s">
+      <c r="B196" s="1" t="s">
         <v>197</v>
       </c>
       <c r="C196" s="2" t="n">
@@ -4351,7 +4342,7 @@
       <c r="A197" s="1" t="n">
         <v>351710</v>
       </c>
-      <c r="B197" s="0" t="s">
+      <c r="B197" s="1" t="s">
         <v>198</v>
       </c>
       <c r="C197" s="2" t="n">
@@ -4362,7 +4353,7 @@
       <c r="A198" s="1" t="n">
         <v>351720</v>
       </c>
-      <c r="B198" s="0" t="s">
+      <c r="B198" s="1" t="s">
         <v>199</v>
       </c>
       <c r="C198" s="2" t="n">
@@ -4373,7 +4364,7 @@
       <c r="A199" s="1" t="n">
         <v>351730</v>
       </c>
-      <c r="B199" s="0" t="s">
+      <c r="B199" s="1" t="s">
         <v>200</v>
       </c>
       <c r="C199" s="2" t="n">
@@ -4384,7 +4375,7 @@
       <c r="A200" s="1" t="n">
         <v>351740</v>
       </c>
-      <c r="B200" s="0" t="s">
+      <c r="B200" s="1" t="s">
         <v>201</v>
       </c>
       <c r="C200" s="2" t="n">
@@ -4395,7 +4386,7 @@
       <c r="A201" s="1" t="n">
         <v>351750</v>
       </c>
-      <c r="B201" s="0" t="s">
+      <c r="B201" s="1" t="s">
         <v>202</v>
       </c>
       <c r="C201" s="2" t="n">
@@ -4406,7 +4397,7 @@
       <c r="A202" s="1" t="n">
         <v>351760</v>
       </c>
-      <c r="B202" s="0" t="s">
+      <c r="B202" s="1" t="s">
         <v>203</v>
       </c>
       <c r="C202" s="2" t="n">
@@ -4417,7 +4408,7 @@
       <c r="A203" s="1" t="n">
         <v>351770</v>
       </c>
-      <c r="B203" s="0" t="s">
+      <c r="B203" s="1" t="s">
         <v>204</v>
       </c>
       <c r="C203" s="2" t="n">
@@ -4428,7 +4419,7 @@
       <c r="A204" s="1" t="n">
         <v>351780</v>
       </c>
-      <c r="B204" s="0" t="s">
+      <c r="B204" s="1" t="s">
         <v>205</v>
       </c>
       <c r="C204" s="2" t="n">
@@ -4439,7 +4430,7 @@
       <c r="A205" s="1" t="n">
         <v>351790</v>
       </c>
-      <c r="B205" s="0" t="s">
+      <c r="B205" s="1" t="s">
         <v>206</v>
       </c>
       <c r="C205" s="2" t="n">
@@ -4450,7 +4441,7 @@
       <c r="A206" s="1" t="n">
         <v>351800</v>
       </c>
-      <c r="B206" s="0" t="s">
+      <c r="B206" s="1" t="s">
         <v>207</v>
       </c>
       <c r="C206" s="2" t="n">
@@ -4461,7 +4452,7 @@
       <c r="A207" s="1" t="n">
         <v>351810</v>
       </c>
-      <c r="B207" s="0" t="s">
+      <c r="B207" s="1" t="s">
         <v>208</v>
       </c>
       <c r="C207" s="2" t="n">
@@ -4472,7 +4463,7 @@
       <c r="A208" s="1" t="n">
         <v>351820</v>
       </c>
-      <c r="B208" s="0" t="s">
+      <c r="B208" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C208" s="2" t="n">
@@ -4483,7 +4474,7 @@
       <c r="A209" s="1" t="n">
         <v>351830</v>
       </c>
-      <c r="B209" s="0" t="s">
+      <c r="B209" s="1" t="s">
         <v>210</v>
       </c>
       <c r="C209" s="2" t="n">
@@ -4494,7 +4485,7 @@
       <c r="A210" s="1" t="n">
         <v>351840</v>
       </c>
-      <c r="B210" s="0" t="s">
+      <c r="B210" s="1" t="s">
         <v>211</v>
       </c>
       <c r="C210" s="2" t="n">
@@ -4505,7 +4496,7 @@
       <c r="A211" s="1" t="n">
         <v>351850</v>
       </c>
-      <c r="B211" s="0" t="s">
+      <c r="B211" s="1" t="s">
         <v>212</v>
       </c>
       <c r="C211" s="2" t="n">
@@ -4516,7 +4507,7 @@
       <c r="A212" s="1" t="n">
         <v>351860</v>
       </c>
-      <c r="B212" s="0" t="s">
+      <c r="B212" s="1" t="s">
         <v>213</v>
       </c>
       <c r="C212" s="2" t="n">
@@ -4527,7 +4518,7 @@
       <c r="A213" s="1" t="n">
         <v>351870</v>
       </c>
-      <c r="B213" s="0" t="s">
+      <c r="B213" s="1" t="s">
         <v>214</v>
       </c>
       <c r="C213" s="2" t="n">
@@ -4538,7 +4529,7 @@
       <c r="A214" s="1" t="n">
         <v>351880</v>
       </c>
-      <c r="B214" s="0" t="s">
+      <c r="B214" s="1" t="s">
         <v>215</v>
       </c>
       <c r="C214" s="2" t="n">
@@ -4549,7 +4540,7 @@
       <c r="A215" s="1" t="n">
         <v>351885</v>
       </c>
-      <c r="B215" s="0" t="s">
+      <c r="B215" s="1" t="s">
         <v>216</v>
       </c>
       <c r="C215" s="2" t="n">
@@ -4560,7 +4551,7 @@
       <c r="A216" s="1" t="n">
         <v>351890</v>
       </c>
-      <c r="B216" s="0" t="s">
+      <c r="B216" s="1" t="s">
         <v>217</v>
       </c>
       <c r="C216" s="2" t="n">
@@ -4571,7 +4562,7 @@
       <c r="A217" s="1" t="n">
         <v>351900</v>
       </c>
-      <c r="B217" s="0" t="s">
+      <c r="B217" s="1" t="s">
         <v>218</v>
       </c>
       <c r="C217" s="2" t="n">
@@ -4582,7 +4573,7 @@
       <c r="A218" s="1" t="n">
         <v>351905</v>
       </c>
-      <c r="B218" s="0" t="s">
+      <c r="B218" s="1" t="s">
         <v>219</v>
       </c>
       <c r="C218" s="2" t="n">
@@ -4593,7 +4584,7 @@
       <c r="A219" s="1" t="n">
         <v>351907</v>
       </c>
-      <c r="B219" s="0" t="s">
+      <c r="B219" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C219" s="2" t="n">
@@ -4604,7 +4595,7 @@
       <c r="A220" s="1" t="n">
         <v>351910</v>
       </c>
-      <c r="B220" s="0" t="s">
+      <c r="B220" s="1" t="s">
         <v>221</v>
       </c>
       <c r="C220" s="2" t="n">
@@ -4615,7 +4606,7 @@
       <c r="A221" s="1" t="n">
         <v>351920</v>
       </c>
-      <c r="B221" s="0" t="s">
+      <c r="B221" s="1" t="s">
         <v>222</v>
       </c>
       <c r="C221" s="2" t="n">
@@ -4626,7 +4617,7 @@
       <c r="A222" s="1" t="n">
         <v>351925</v>
       </c>
-      <c r="B222" s="0" t="s">
+      <c r="B222" s="1" t="s">
         <v>223</v>
       </c>
       <c r="C222" s="2" t="n">
@@ -4637,7 +4628,7 @@
       <c r="A223" s="1" t="n">
         <v>351930</v>
       </c>
-      <c r="B223" s="0" t="s">
+      <c r="B223" s="1" t="s">
         <v>224</v>
       </c>
       <c r="C223" s="2" t="n">
@@ -4648,7 +4639,7 @@
       <c r="A224" s="1" t="n">
         <v>351940</v>
       </c>
-      <c r="B224" s="0" t="s">
+      <c r="B224" s="1" t="s">
         <v>225</v>
       </c>
       <c r="C224" s="2" t="n">
@@ -4659,7 +4650,7 @@
       <c r="A225" s="1" t="n">
         <v>351950</v>
       </c>
-      <c r="B225" s="0" t="s">
+      <c r="B225" s="1" t="s">
         <v>226</v>
       </c>
       <c r="C225" s="2" t="n">
@@ -4670,7 +4661,7 @@
       <c r="A226" s="1" t="n">
         <v>351960</v>
       </c>
-      <c r="B226" s="0" t="s">
+      <c r="B226" s="1" t="s">
         <v>227</v>
       </c>
       <c r="C226" s="2" t="n">
@@ -4681,7 +4672,7 @@
       <c r="A227" s="1" t="n">
         <v>351970</v>
       </c>
-      <c r="B227" s="0" t="s">
+      <c r="B227" s="1" t="s">
         <v>228</v>
       </c>
       <c r="C227" s="2" t="n">
@@ -4692,7 +4683,7 @@
       <c r="A228" s="1" t="n">
         <v>351980</v>
       </c>
-      <c r="B228" s="0" t="s">
+      <c r="B228" s="1" t="s">
         <v>229</v>
       </c>
       <c r="C228" s="2" t="n">
@@ -4703,7 +4694,7 @@
       <c r="A229" s="1" t="n">
         <v>351990</v>
       </c>
-      <c r="B229" s="0" t="s">
+      <c r="B229" s="1" t="s">
         <v>230</v>
       </c>
       <c r="C229" s="2" t="n">
@@ -4714,7 +4705,7 @@
       <c r="A230" s="1" t="n">
         <v>352000</v>
       </c>
-      <c r="B230" s="0" t="s">
+      <c r="B230" s="1" t="s">
         <v>231</v>
       </c>
       <c r="C230" s="2" t="n">
@@ -4725,7 +4716,7 @@
       <c r="A231" s="1" t="n">
         <v>352010</v>
       </c>
-      <c r="B231" s="0" t="s">
+      <c r="B231" s="1" t="s">
         <v>232</v>
       </c>
       <c r="C231" s="2" t="n">
@@ -4736,7 +4727,7 @@
       <c r="A232" s="1" t="n">
         <v>352020</v>
       </c>
-      <c r="B232" s="0" t="s">
+      <c r="B232" s="1" t="s">
         <v>233</v>
       </c>
       <c r="C232" s="2" t="n">
@@ -4747,7 +4738,7 @@
       <c r="A233" s="1" t="n">
         <v>352030</v>
       </c>
-      <c r="B233" s="0" t="s">
+      <c r="B233" s="1" t="s">
         <v>234</v>
       </c>
       <c r="C233" s="2" t="n">
@@ -4758,7 +4749,7 @@
       <c r="A234" s="1" t="n">
         <v>352040</v>
       </c>
-      <c r="B234" s="0" t="s">
+      <c r="B234" s="1" t="s">
         <v>235</v>
       </c>
       <c r="C234" s="2" t="n">
@@ -4769,7 +4760,7 @@
       <c r="A235" s="1" t="n">
         <v>352042</v>
       </c>
-      <c r="B235" s="0" t="s">
+      <c r="B235" s="1" t="s">
         <v>236</v>
       </c>
       <c r="C235" s="2" t="n">
@@ -4780,7 +4771,7 @@
       <c r="A236" s="1" t="n">
         <v>352044</v>
       </c>
-      <c r="B236" s="0" t="s">
+      <c r="B236" s="1" t="s">
         <v>237</v>
       </c>
       <c r="C236" s="2" t="n">
@@ -4791,7 +4782,7 @@
       <c r="A237" s="1" t="n">
         <v>352050</v>
       </c>
-      <c r="B237" s="0" t="s">
+      <c r="B237" s="1" t="s">
         <v>238</v>
       </c>
       <c r="C237" s="2" t="n">
@@ -4802,7 +4793,7 @@
       <c r="A238" s="1" t="n">
         <v>352060</v>
       </c>
-      <c r="B238" s="0" t="s">
+      <c r="B238" s="1" t="s">
         <v>239</v>
       </c>
       <c r="C238" s="2" t="n">
@@ -4813,7 +4804,7 @@
       <c r="A239" s="1" t="n">
         <v>352070</v>
       </c>
-      <c r="B239" s="0" t="s">
+      <c r="B239" s="1" t="s">
         <v>240</v>
       </c>
       <c r="C239" s="2" t="n">
@@ -4824,7 +4815,7 @@
       <c r="A240" s="1" t="n">
         <v>352080</v>
       </c>
-      <c r="B240" s="0" t="s">
+      <c r="B240" s="1" t="s">
         <v>241</v>
       </c>
       <c r="C240" s="2" t="n">
@@ -4835,7 +4826,7 @@
       <c r="A241" s="1" t="n">
         <v>352090</v>
       </c>
-      <c r="B241" s="0" t="s">
+      <c r="B241" s="1" t="s">
         <v>242</v>
       </c>
       <c r="C241" s="2" t="n">
@@ -4846,7 +4837,7 @@
       <c r="A242" s="1" t="n">
         <v>352100</v>
       </c>
-      <c r="B242" s="0" t="s">
+      <c r="B242" s="1" t="s">
         <v>243</v>
       </c>
       <c r="C242" s="2" t="n">
@@ -4857,7 +4848,7 @@
       <c r="A243" s="1" t="n">
         <v>352110</v>
       </c>
-      <c r="B243" s="0" t="s">
+      <c r="B243" s="1" t="s">
         <v>244</v>
       </c>
       <c r="C243" s="2" t="n">
@@ -4868,7 +4859,7 @@
       <c r="A244" s="1" t="n">
         <v>352115</v>
       </c>
-      <c r="B244" s="0" t="s">
+      <c r="B244" s="1" t="s">
         <v>245</v>
       </c>
       <c r="C244" s="2" t="n">
@@ -4879,7 +4870,7 @@
       <c r="A245" s="1" t="n">
         <v>352120</v>
       </c>
-      <c r="B245" s="0" t="s">
+      <c r="B245" s="1" t="s">
         <v>246</v>
       </c>
       <c r="C245" s="2" t="n">
@@ -4890,7 +4881,7 @@
       <c r="A246" s="1" t="n">
         <v>352130</v>
       </c>
-      <c r="B246" s="0" t="s">
+      <c r="B246" s="1" t="s">
         <v>247</v>
       </c>
       <c r="C246" s="2" t="n">
@@ -4901,7 +4892,7 @@
       <c r="A247" s="1" t="n">
         <v>352140</v>
       </c>
-      <c r="B247" s="0" t="s">
+      <c r="B247" s="1" t="s">
         <v>248</v>
       </c>
       <c r="C247" s="2" t="n">
@@ -4912,7 +4903,7 @@
       <c r="A248" s="1" t="n">
         <v>352150</v>
       </c>
-      <c r="B248" s="0" t="s">
+      <c r="B248" s="1" t="s">
         <v>249</v>
       </c>
       <c r="C248" s="2" t="n">
@@ -4923,7 +4914,7 @@
       <c r="A249" s="1" t="n">
         <v>352160</v>
       </c>
-      <c r="B249" s="0" t="s">
+      <c r="B249" s="1" t="s">
         <v>250</v>
       </c>
       <c r="C249" s="2" t="n">
@@ -4934,7 +4925,7 @@
       <c r="A250" s="1" t="n">
         <v>352170</v>
       </c>
-      <c r="B250" s="0" t="s">
+      <c r="B250" s="1" t="s">
         <v>251</v>
       </c>
       <c r="C250" s="2" t="n">
@@ -4945,7 +4936,7 @@
       <c r="A251" s="1" t="n">
         <v>352180</v>
       </c>
-      <c r="B251" s="0" t="s">
+      <c r="B251" s="1" t="s">
         <v>252</v>
       </c>
       <c r="C251" s="2" t="n">
@@ -4956,7 +4947,7 @@
       <c r="A252" s="1" t="n">
         <v>352190</v>
       </c>
-      <c r="B252" s="0" t="s">
+      <c r="B252" s="1" t="s">
         <v>253</v>
       </c>
       <c r="C252" s="2" t="n">
@@ -4967,7 +4958,7 @@
       <c r="A253" s="1" t="n">
         <v>352200</v>
       </c>
-      <c r="B253" s="0" t="s">
+      <c r="B253" s="1" t="s">
         <v>254</v>
       </c>
       <c r="C253" s="2" t="n">
@@ -4978,7 +4969,7 @@
       <c r="A254" s="1" t="n">
         <v>352210</v>
       </c>
-      <c r="B254" s="0" t="s">
+      <c r="B254" s="1" t="s">
         <v>255</v>
       </c>
       <c r="C254" s="2" t="n">
@@ -4989,7 +4980,7 @@
       <c r="A255" s="1" t="n">
         <v>352215</v>
       </c>
-      <c r="B255" s="0" t="s">
+      <c r="B255" s="1" t="s">
         <v>256</v>
       </c>
       <c r="C255" s="2" t="n">
@@ -5000,7 +4991,7 @@
       <c r="A256" s="1" t="n">
         <v>352220</v>
       </c>
-      <c r="B256" s="0" t="s">
+      <c r="B256" s="1" t="s">
         <v>257</v>
       </c>
       <c r="C256" s="2" t="n">
@@ -5011,7 +5002,7 @@
       <c r="A257" s="1" t="n">
         <v>352230</v>
       </c>
-      <c r="B257" s="0" t="s">
+      <c r="B257" s="1" t="s">
         <v>258</v>
       </c>
       <c r="C257" s="2" t="n">
@@ -5022,7 +5013,7 @@
       <c r="A258" s="1" t="n">
         <v>352240</v>
       </c>
-      <c r="B258" s="0" t="s">
+      <c r="B258" s="1" t="s">
         <v>259</v>
       </c>
       <c r="C258" s="2" t="n">
@@ -5033,7 +5024,7 @@
       <c r="A259" s="1" t="n">
         <v>352250</v>
       </c>
-      <c r="B259" s="0" t="s">
+      <c r="B259" s="1" t="s">
         <v>260</v>
       </c>
       <c r="C259" s="2" t="n">
@@ -5044,7 +5035,7 @@
       <c r="A260" s="1" t="n">
         <v>352260</v>
       </c>
-      <c r="B260" s="0" t="s">
+      <c r="B260" s="1" t="s">
         <v>261</v>
       </c>
       <c r="C260" s="2" t="n">
@@ -5055,7 +5046,7 @@
       <c r="A261" s="1" t="n">
         <v>352265</v>
       </c>
-      <c r="B261" s="0" t="s">
+      <c r="B261" s="1" t="s">
         <v>262</v>
       </c>
       <c r="C261" s="2" t="n">
@@ -5066,7 +5057,7 @@
       <c r="A262" s="1" t="n">
         <v>352270</v>
       </c>
-      <c r="B262" s="0" t="s">
+      <c r="B262" s="1" t="s">
         <v>263</v>
       </c>
       <c r="C262" s="2" t="n">
@@ -5077,7 +5068,7 @@
       <c r="A263" s="1" t="n">
         <v>352280</v>
       </c>
-      <c r="B263" s="0" t="s">
+      <c r="B263" s="1" t="s">
         <v>264</v>
       </c>
       <c r="C263" s="2" t="n">
@@ -5088,7 +5079,7 @@
       <c r="A264" s="1" t="n">
         <v>352290</v>
       </c>
-      <c r="B264" s="0" t="s">
+      <c r="B264" s="1" t="s">
         <v>265</v>
       </c>
       <c r="C264" s="2" t="n">
@@ -5099,7 +5090,7 @@
       <c r="A265" s="1" t="n">
         <v>352300</v>
       </c>
-      <c r="B265" s="0" t="s">
+      <c r="B265" s="1" t="s">
         <v>266</v>
       </c>
       <c r="C265" s="2" t="n">
@@ -5110,7 +5101,7 @@
       <c r="A266" s="1" t="n">
         <v>352310</v>
       </c>
-      <c r="B266" s="0" t="s">
+      <c r="B266" s="1" t="s">
         <v>267</v>
       </c>
       <c r="C266" s="2" t="n">
@@ -5121,7 +5112,7 @@
       <c r="A267" s="1" t="n">
         <v>352320</v>
       </c>
-      <c r="B267" s="0" t="s">
+      <c r="B267" s="1" t="s">
         <v>268</v>
       </c>
       <c r="C267" s="2" t="n">
@@ -5132,7 +5123,7 @@
       <c r="A268" s="1" t="n">
         <v>352330</v>
       </c>
-      <c r="B268" s="0" t="s">
+      <c r="B268" s="1" t="s">
         <v>269</v>
       </c>
       <c r="C268" s="2" t="n">
@@ -5143,7 +5134,7 @@
       <c r="A269" s="1" t="n">
         <v>352340</v>
       </c>
-      <c r="B269" s="0" t="s">
+      <c r="B269" s="1" t="s">
         <v>270</v>
       </c>
       <c r="C269" s="2" t="n">
@@ -5154,7 +5145,7 @@
       <c r="A270" s="1" t="n">
         <v>352350</v>
       </c>
-      <c r="B270" s="0" t="s">
+      <c r="B270" s="1" t="s">
         <v>271</v>
       </c>
       <c r="C270" s="2" t="n">
@@ -5165,7 +5156,7 @@
       <c r="A271" s="1" t="n">
         <v>352360</v>
       </c>
-      <c r="B271" s="0" t="s">
+      <c r="B271" s="1" t="s">
         <v>272</v>
       </c>
       <c r="C271" s="2" t="n">
@@ -5176,7 +5167,7 @@
       <c r="A272" s="1" t="n">
         <v>352370</v>
       </c>
-      <c r="B272" s="0" t="s">
+      <c r="B272" s="1" t="s">
         <v>273</v>
       </c>
       <c r="C272" s="2" t="n">
@@ -5187,7 +5178,7 @@
       <c r="A273" s="1" t="n">
         <v>352380</v>
       </c>
-      <c r="B273" s="0" t="s">
+      <c r="B273" s="1" t="s">
         <v>274</v>
       </c>
       <c r="C273" s="2" t="n">
@@ -5198,7 +5189,7 @@
       <c r="A274" s="1" t="n">
         <v>352390</v>
       </c>
-      <c r="B274" s="0" t="s">
+      <c r="B274" s="1" t="s">
         <v>275</v>
       </c>
       <c r="C274" s="2" t="n">
@@ -5209,7 +5200,7 @@
       <c r="A275" s="1" t="n">
         <v>352400</v>
       </c>
-      <c r="B275" s="0" t="s">
+      <c r="B275" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C275" s="2" t="n">
@@ -5220,7 +5211,7 @@
       <c r="A276" s="1" t="n">
         <v>352410</v>
       </c>
-      <c r="B276" s="0" t="s">
+      <c r="B276" s="1" t="s">
         <v>277</v>
       </c>
       <c r="C276" s="2" t="n">
@@ -5231,7 +5222,7 @@
       <c r="A277" s="1" t="n">
         <v>352420</v>
       </c>
-      <c r="B277" s="0" t="s">
+      <c r="B277" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C277" s="2" t="n">
@@ -5242,7 +5233,7 @@
       <c r="A278" s="1" t="n">
         <v>352430</v>
       </c>
-      <c r="B278" s="0" t="s">
+      <c r="B278" s="1" t="s">
         <v>279</v>
       </c>
       <c r="C278" s="2" t="n">
@@ -5253,7 +5244,7 @@
       <c r="A279" s="1" t="n">
         <v>352440</v>
       </c>
-      <c r="B279" s="0" t="s">
+      <c r="B279" s="1" t="s">
         <v>280</v>
       </c>
       <c r="C279" s="2" t="n">
@@ -5264,7 +5255,7 @@
       <c r="A280" s="1" t="n">
         <v>352450</v>
       </c>
-      <c r="B280" s="0" t="s">
+      <c r="B280" s="1" t="s">
         <v>281</v>
       </c>
       <c r="C280" s="2" t="n">
@@ -5275,7 +5266,7 @@
       <c r="A281" s="1" t="n">
         <v>352460</v>
       </c>
-      <c r="B281" s="0" t="s">
+      <c r="B281" s="1" t="s">
         <v>282</v>
       </c>
       <c r="C281" s="2" t="n">
@@ -5286,7 +5277,7 @@
       <c r="A282" s="1" t="n">
         <v>352470</v>
       </c>
-      <c r="B282" s="0" t="s">
+      <c r="B282" s="1" t="s">
         <v>283</v>
       </c>
       <c r="C282" s="2" t="n">
@@ -5297,7 +5288,7 @@
       <c r="A283" s="1" t="n">
         <v>352480</v>
       </c>
-      <c r="B283" s="0" t="s">
+      <c r="B283" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C283" s="2" t="n">
@@ -5308,7 +5299,7 @@
       <c r="A284" s="1" t="n">
         <v>352490</v>
       </c>
-      <c r="B284" s="0" t="s">
+      <c r="B284" s="1" t="s">
         <v>285</v>
       </c>
       <c r="C284" s="2" t="n">
@@ -5319,7 +5310,7 @@
       <c r="A285" s="1" t="n">
         <v>352500</v>
       </c>
-      <c r="B285" s="0" t="s">
+      <c r="B285" s="1" t="s">
         <v>286</v>
       </c>
       <c r="C285" s="2" t="n">
@@ -5330,7 +5321,7 @@
       <c r="A286" s="1" t="n">
         <v>352510</v>
       </c>
-      <c r="B286" s="0" t="s">
+      <c r="B286" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C286" s="2" t="n">
@@ -5341,7 +5332,7 @@
       <c r="A287" s="1" t="n">
         <v>352520</v>
       </c>
-      <c r="B287" s="0" t="s">
+      <c r="B287" s="1" t="s">
         <v>288</v>
       </c>
       <c r="C287" s="2" t="n">
@@ -5352,7 +5343,7 @@
       <c r="A288" s="1" t="n">
         <v>352530</v>
       </c>
-      <c r="B288" s="0" t="s">
+      <c r="B288" s="1" t="s">
         <v>289</v>
       </c>
       <c r="C288" s="2" t="n">
@@ -5363,7 +5354,7 @@
       <c r="A289" s="1" t="n">
         <v>352540</v>
       </c>
-      <c r="B289" s="0" t="s">
+      <c r="B289" s="1" t="s">
         <v>290</v>
       </c>
       <c r="C289" s="2" t="n">
@@ -5374,7 +5365,7 @@
       <c r="A290" s="1" t="n">
         <v>352550</v>
       </c>
-      <c r="B290" s="0" t="s">
+      <c r="B290" s="1" t="s">
         <v>291</v>
       </c>
       <c r="C290" s="2" t="n">
@@ -5385,7 +5376,7 @@
       <c r="A291" s="1" t="n">
         <v>352560</v>
       </c>
-      <c r="B291" s="0" t="s">
+      <c r="B291" s="1" t="s">
         <v>292</v>
       </c>
       <c r="C291" s="2" t="n">
@@ -5396,7 +5387,7 @@
       <c r="A292" s="1" t="n">
         <v>352570</v>
       </c>
-      <c r="B292" s="0" t="s">
+      <c r="B292" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C292" s="2" t="n">
@@ -5407,7 +5398,7 @@
       <c r="A293" s="1" t="n">
         <v>352580</v>
       </c>
-      <c r="B293" s="0" t="s">
+      <c r="B293" s="1" t="s">
         <v>294</v>
       </c>
       <c r="C293" s="2" t="n">
@@ -5418,7 +5409,7 @@
       <c r="A294" s="1" t="n">
         <v>352585</v>
       </c>
-      <c r="B294" s="0" t="s">
+      <c r="B294" s="1" t="s">
         <v>295</v>
       </c>
       <c r="C294" s="2" t="n">
@@ -5429,7 +5420,7 @@
       <c r="A295" s="1" t="n">
         <v>352590</v>
       </c>
-      <c r="B295" s="0" t="s">
+      <c r="B295" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C295" s="2" t="n">
@@ -5440,7 +5431,7 @@
       <c r="A296" s="1" t="n">
         <v>352600</v>
       </c>
-      <c r="B296" s="0" t="s">
+      <c r="B296" s="1" t="s">
         <v>297</v>
       </c>
       <c r="C296" s="2" t="n">
@@ -5451,7 +5442,7 @@
       <c r="A297" s="1" t="n">
         <v>352610</v>
       </c>
-      <c r="B297" s="0" t="s">
+      <c r="B297" s="1" t="s">
         <v>298</v>
       </c>
       <c r="C297" s="2" t="n">
@@ -5462,7 +5453,7 @@
       <c r="A298" s="1" t="n">
         <v>352620</v>
       </c>
-      <c r="B298" s="0" t="s">
+      <c r="B298" s="1" t="s">
         <v>299</v>
       </c>
       <c r="C298" s="2" t="n">
@@ -5473,7 +5464,7 @@
       <c r="A299" s="1" t="n">
         <v>352630</v>
       </c>
-      <c r="B299" s="0" t="s">
+      <c r="B299" s="1" t="s">
         <v>300</v>
       </c>
       <c r="C299" s="2" t="n">
@@ -5484,7 +5475,7 @@
       <c r="A300" s="1" t="n">
         <v>352640</v>
       </c>
-      <c r="B300" s="0" t="s">
+      <c r="B300" s="1" t="s">
         <v>301</v>
       </c>
       <c r="C300" s="2" t="n">
@@ -5495,7 +5486,7 @@
       <c r="A301" s="1" t="n">
         <v>352650</v>
       </c>
-      <c r="B301" s="0" t="s">
+      <c r="B301" s="1" t="s">
         <v>302</v>
       </c>
       <c r="C301" s="2" t="n">
@@ -5506,7 +5497,7 @@
       <c r="A302" s="1" t="n">
         <v>352660</v>
       </c>
-      <c r="B302" s="0" t="s">
+      <c r="B302" s="1" t="s">
         <v>303</v>
       </c>
       <c r="C302" s="2" t="n">
@@ -5517,7 +5508,7 @@
       <c r="A303" s="1" t="n">
         <v>352670</v>
       </c>
-      <c r="B303" s="0" t="s">
+      <c r="B303" s="1" t="s">
         <v>304</v>
       </c>
       <c r="C303" s="2" t="n">
@@ -5528,7 +5519,7 @@
       <c r="A304" s="1" t="n">
         <v>352680</v>
       </c>
-      <c r="B304" s="0" t="s">
+      <c r="B304" s="1" t="s">
         <v>305</v>
       </c>
       <c r="C304" s="2" t="n">
@@ -5539,7 +5530,7 @@
       <c r="A305" s="1" t="n">
         <v>352690</v>
       </c>
-      <c r="B305" s="0" t="s">
+      <c r="B305" s="1" t="s">
         <v>306</v>
       </c>
       <c r="C305" s="2" t="n">
@@ -5550,7 +5541,7 @@
       <c r="A306" s="1" t="n">
         <v>352700</v>
       </c>
-      <c r="B306" s="0" t="s">
+      <c r="B306" s="1" t="s">
         <v>307</v>
       </c>
       <c r="C306" s="2" t="n">
@@ -5561,7 +5552,7 @@
       <c r="A307" s="1" t="n">
         <v>352710</v>
       </c>
-      <c r="B307" s="0" t="s">
+      <c r="B307" s="1" t="s">
         <v>308</v>
       </c>
       <c r="C307" s="2" t="n">
@@ -5572,7 +5563,7 @@
       <c r="A308" s="1" t="n">
         <v>352720</v>
       </c>
-      <c r="B308" s="0" t="s">
+      <c r="B308" s="1" t="s">
         <v>309</v>
       </c>
       <c r="C308" s="2" t="n">
@@ -5583,7 +5574,7 @@
       <c r="A309" s="1" t="n">
         <v>352725</v>
       </c>
-      <c r="B309" s="0" t="s">
+      <c r="B309" s="1" t="s">
         <v>310</v>
       </c>
       <c r="C309" s="2" t="n">
@@ -5594,7 +5585,7 @@
       <c r="A310" s="1" t="n">
         <v>352730</v>
       </c>
-      <c r="B310" s="0" t="s">
+      <c r="B310" s="1" t="s">
         <v>311</v>
       </c>
       <c r="C310" s="2" t="n">
@@ -5605,7 +5596,7 @@
       <c r="A311" s="1" t="n">
         <v>352740</v>
       </c>
-      <c r="B311" s="0" t="s">
+      <c r="B311" s="1" t="s">
         <v>312</v>
       </c>
       <c r="C311" s="2" t="n">
@@ -5616,7 +5607,7 @@
       <c r="A312" s="1" t="n">
         <v>352750</v>
       </c>
-      <c r="B312" s="0" t="s">
+      <c r="B312" s="1" t="s">
         <v>313</v>
       </c>
       <c r="C312" s="2" t="n">
@@ -5627,7 +5618,7 @@
       <c r="A313" s="1" t="n">
         <v>352760</v>
       </c>
-      <c r="B313" s="0" t="s">
+      <c r="B313" s="1" t="s">
         <v>314</v>
       </c>
       <c r="C313" s="2" t="n">
@@ -5638,7 +5629,7 @@
       <c r="A314" s="1" t="n">
         <v>352770</v>
       </c>
-      <c r="B314" s="0" t="s">
+      <c r="B314" s="1" t="s">
         <v>315</v>
       </c>
       <c r="C314" s="2" t="n">
@@ -5649,7 +5640,7 @@
       <c r="A315" s="1" t="n">
         <v>352780</v>
       </c>
-      <c r="B315" s="0" t="s">
+      <c r="B315" s="1" t="s">
         <v>316</v>
       </c>
       <c r="C315" s="2" t="n">
@@ -5660,7 +5651,7 @@
       <c r="A316" s="1" t="n">
         <v>352790</v>
       </c>
-      <c r="B316" s="0" t="s">
+      <c r="B316" s="1" t="s">
         <v>317</v>
       </c>
       <c r="C316" s="2" t="n">
@@ -5671,7 +5662,7 @@
       <c r="A317" s="1" t="n">
         <v>352800</v>
       </c>
-      <c r="B317" s="0" t="s">
+      <c r="B317" s="1" t="s">
         <v>318</v>
       </c>
       <c r="C317" s="2" t="n">
@@ -5682,7 +5673,7 @@
       <c r="A318" s="1" t="n">
         <v>352810</v>
       </c>
-      <c r="B318" s="0" t="s">
+      <c r="B318" s="1" t="s">
         <v>319</v>
       </c>
       <c r="C318" s="2" t="n">
@@ -5693,7 +5684,7 @@
       <c r="A319" s="1" t="n">
         <v>352820</v>
       </c>
-      <c r="B319" s="0" t="s">
+      <c r="B319" s="1" t="s">
         <v>320</v>
       </c>
       <c r="C319" s="2" t="n">
@@ -5704,7 +5695,7 @@
       <c r="A320" s="1" t="n">
         <v>352830</v>
       </c>
-      <c r="B320" s="0" t="s">
+      <c r="B320" s="1" t="s">
         <v>321</v>
       </c>
       <c r="C320" s="2" t="n">
@@ -5715,7 +5706,7 @@
       <c r="A321" s="1" t="n">
         <v>352840</v>
       </c>
-      <c r="B321" s="0" t="s">
+      <c r="B321" s="1" t="s">
         <v>322</v>
       </c>
       <c r="C321" s="2" t="n">
@@ -5726,7 +5717,7 @@
       <c r="A322" s="1" t="n">
         <v>352850</v>
       </c>
-      <c r="B322" s="0" t="s">
+      <c r="B322" s="1" t="s">
         <v>323</v>
       </c>
       <c r="C322" s="2" t="n">
@@ -5737,7 +5728,7 @@
       <c r="A323" s="1" t="n">
         <v>352860</v>
       </c>
-      <c r="B323" s="0" t="s">
+      <c r="B323" s="1" t="s">
         <v>324</v>
       </c>
       <c r="C323" s="2" t="n">
@@ -5748,7 +5739,7 @@
       <c r="A324" s="1" t="n">
         <v>352870</v>
       </c>
-      <c r="B324" s="0" t="s">
+      <c r="B324" s="1" t="s">
         <v>325</v>
       </c>
       <c r="C324" s="2" t="n">
@@ -5759,7 +5750,7 @@
       <c r="A325" s="1" t="n">
         <v>352880</v>
       </c>
-      <c r="B325" s="0" t="s">
+      <c r="B325" s="1" t="s">
         <v>326</v>
       </c>
       <c r="C325" s="2" t="n">
@@ -5770,7 +5761,7 @@
       <c r="A326" s="1" t="n">
         <v>352885</v>
       </c>
-      <c r="B326" s="0" t="s">
+      <c r="B326" s="1" t="s">
         <v>327</v>
       </c>
       <c r="C326" s="2" t="n">
@@ -5781,7 +5772,7 @@
       <c r="A327" s="1" t="n">
         <v>352890</v>
       </c>
-      <c r="B327" s="0" t="s">
+      <c r="B327" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C327" s="2" t="n">
@@ -5792,7 +5783,7 @@
       <c r="A328" s="1" t="n">
         <v>352900</v>
       </c>
-      <c r="B328" s="0" t="s">
+      <c r="B328" s="1" t="s">
         <v>329</v>
       </c>
       <c r="C328" s="2" t="n">
@@ -5803,7 +5794,7 @@
       <c r="A329" s="1" t="n">
         <v>352910</v>
       </c>
-      <c r="B329" s="0" t="s">
+      <c r="B329" s="1" t="s">
         <v>330</v>
       </c>
       <c r="C329" s="2" t="n">
@@ -5814,7 +5805,7 @@
       <c r="A330" s="1" t="n">
         <v>352920</v>
       </c>
-      <c r="B330" s="0" t="s">
+      <c r="B330" s="1" t="s">
         <v>331</v>
       </c>
       <c r="C330" s="2" t="n">
@@ -5825,7 +5816,7 @@
       <c r="A331" s="1" t="n">
         <v>352930</v>
       </c>
-      <c r="B331" s="0" t="s">
+      <c r="B331" s="1" t="s">
         <v>332</v>
       </c>
       <c r="C331" s="2" t="n">
@@ -5836,7 +5827,7 @@
       <c r="A332" s="1" t="n">
         <v>352940</v>
       </c>
-      <c r="B332" s="0" t="s">
+      <c r="B332" s="1" t="s">
         <v>333</v>
       </c>
       <c r="C332" s="2" t="n">
@@ -5847,7 +5838,7 @@
       <c r="A333" s="1" t="n">
         <v>352950</v>
       </c>
-      <c r="B333" s="0" t="s">
+      <c r="B333" s="1" t="s">
         <v>334</v>
       </c>
       <c r="C333" s="2" t="n">
@@ -5858,7 +5849,7 @@
       <c r="A334" s="1" t="n">
         <v>352960</v>
       </c>
-      <c r="B334" s="0" t="s">
+      <c r="B334" s="1" t="s">
         <v>335</v>
       </c>
       <c r="C334" s="2" t="n">
@@ -5869,7 +5860,7 @@
       <c r="A335" s="1" t="n">
         <v>352965</v>
       </c>
-      <c r="B335" s="0" t="s">
+      <c r="B335" s="1" t="s">
         <v>336</v>
       </c>
       <c r="C335" s="2" t="n">
@@ -5880,7 +5871,7 @@
       <c r="A336" s="1" t="n">
         <v>352970</v>
       </c>
-      <c r="B336" s="0" t="s">
+      <c r="B336" s="1" t="s">
         <v>337</v>
       </c>
       <c r="C336" s="2" t="n">
@@ -5891,7 +5882,7 @@
       <c r="A337" s="1" t="n">
         <v>352980</v>
       </c>
-      <c r="B337" s="0" t="s">
+      <c r="B337" s="1" t="s">
         <v>338</v>
       </c>
       <c r="C337" s="2" t="n">
@@ -5902,7 +5893,7 @@
       <c r="A338" s="1" t="n">
         <v>352990</v>
       </c>
-      <c r="B338" s="0" t="s">
+      <c r="B338" s="1" t="s">
         <v>339</v>
       </c>
       <c r="C338" s="2" t="n">
@@ -5913,7 +5904,7 @@
       <c r="A339" s="1" t="n">
         <v>353000</v>
       </c>
-      <c r="B339" s="0" t="s">
+      <c r="B339" s="1" t="s">
         <v>340</v>
       </c>
       <c r="C339" s="2" t="n">
@@ -5924,7 +5915,7 @@
       <c r="A340" s="1" t="n">
         <v>353010</v>
       </c>
-      <c r="B340" s="0" t="s">
+      <c r="B340" s="1" t="s">
         <v>341</v>
       </c>
       <c r="C340" s="2" t="n">
@@ -5935,7 +5926,7 @@
       <c r="A341" s="1" t="n">
         <v>353020</v>
       </c>
-      <c r="B341" s="0" t="s">
+      <c r="B341" s="1" t="s">
         <v>342</v>
       </c>
       <c r="C341" s="2" t="n">
@@ -5946,7 +5937,7 @@
       <c r="A342" s="1" t="n">
         <v>353030</v>
       </c>
-      <c r="B342" s="0" t="s">
+      <c r="B342" s="1" t="s">
         <v>343</v>
       </c>
       <c r="C342" s="2" t="n">
@@ -5957,7 +5948,7 @@
       <c r="A343" s="1" t="n">
         <v>353040</v>
       </c>
-      <c r="B343" s="0" t="s">
+      <c r="B343" s="1" t="s">
         <v>344</v>
       </c>
       <c r="C343" s="2" t="n">
@@ -5968,7 +5959,7 @@
       <c r="A344" s="1" t="n">
         <v>353050</v>
       </c>
-      <c r="B344" s="0" t="s">
+      <c r="B344" s="1" t="s">
         <v>345</v>
       </c>
       <c r="C344" s="2" t="n">
@@ -5979,7 +5970,7 @@
       <c r="A345" s="1" t="n">
         <v>353060</v>
       </c>
-      <c r="B345" s="0" t="s">
+      <c r="B345" s="1" t="s">
         <v>346</v>
       </c>
       <c r="C345" s="2" t="n">
@@ -5990,7 +5981,7 @@
       <c r="A346" s="1" t="n">
         <v>353070</v>
       </c>
-      <c r="B346" s="0" t="s">
+      <c r="B346" s="1" t="s">
         <v>347</v>
       </c>
       <c r="C346" s="2" t="n">
@@ -6001,7 +5992,7 @@
       <c r="A347" s="1" t="n">
         <v>353080</v>
       </c>
-      <c r="B347" s="0" t="s">
+      <c r="B347" s="1" t="s">
         <v>348</v>
       </c>
       <c r="C347" s="2" t="n">
@@ -6012,7 +6003,7 @@
       <c r="A348" s="1" t="n">
         <v>353090</v>
       </c>
-      <c r="B348" s="0" t="s">
+      <c r="B348" s="1" t="s">
         <v>349</v>
       </c>
       <c r="C348" s="2" t="n">
@@ -6023,7 +6014,7 @@
       <c r="A349" s="1" t="n">
         <v>353100</v>
       </c>
-      <c r="B349" s="0" t="s">
+      <c r="B349" s="1" t="s">
         <v>350</v>
       </c>
       <c r="C349" s="2" t="n">
@@ -6034,7 +6025,7 @@
       <c r="A350" s="1" t="n">
         <v>353110</v>
       </c>
-      <c r="B350" s="0" t="s">
+      <c r="B350" s="1" t="s">
         <v>351</v>
       </c>
       <c r="C350" s="2" t="n">
@@ -6045,7 +6036,7 @@
       <c r="A351" s="1" t="n">
         <v>353120</v>
       </c>
-      <c r="B351" s="0" t="s">
+      <c r="B351" s="1" t="s">
         <v>352</v>
       </c>
       <c r="C351" s="2" t="n">
@@ -6056,7 +6047,7 @@
       <c r="A352" s="1" t="n">
         <v>353130</v>
       </c>
-      <c r="B352" s="0" t="s">
+      <c r="B352" s="1" t="s">
         <v>353</v>
       </c>
       <c r="C352" s="2" t="n">
@@ -6067,7 +6058,7 @@
       <c r="A353" s="1" t="n">
         <v>353140</v>
       </c>
-      <c r="B353" s="0" t="s">
+      <c r="B353" s="1" t="s">
         <v>354</v>
       </c>
       <c r="C353" s="2" t="n">
@@ -6078,7 +6069,7 @@
       <c r="A354" s="1" t="n">
         <v>353150</v>
       </c>
-      <c r="B354" s="0" t="s">
+      <c r="B354" s="1" t="s">
         <v>355</v>
       </c>
       <c r="C354" s="2" t="n">
@@ -6089,7 +6080,7 @@
       <c r="A355" s="1" t="n">
         <v>353160</v>
       </c>
-      <c r="B355" s="0" t="s">
+      <c r="B355" s="1" t="s">
         <v>356</v>
       </c>
       <c r="C355" s="2" t="n">
@@ -6100,7 +6091,7 @@
       <c r="A356" s="1" t="n">
         <v>353170</v>
       </c>
-      <c r="B356" s="0" t="s">
+      <c r="B356" s="1" t="s">
         <v>357</v>
       </c>
       <c r="C356" s="2" t="n">
@@ -6111,7 +6102,7 @@
       <c r="A357" s="1" t="n">
         <v>353180</v>
       </c>
-      <c r="B357" s="0" t="s">
+      <c r="B357" s="1" t="s">
         <v>358</v>
       </c>
       <c r="C357" s="2" t="n">
@@ -6122,7 +6113,7 @@
       <c r="A358" s="1" t="n">
         <v>353190</v>
       </c>
-      <c r="B358" s="0" t="s">
+      <c r="B358" s="1" t="s">
         <v>359</v>
       </c>
       <c r="C358" s="2" t="n">
@@ -6133,7 +6124,7 @@
       <c r="A359" s="1" t="n">
         <v>353200</v>
       </c>
-      <c r="B359" s="0" t="s">
+      <c r="B359" s="1" t="s">
         <v>360</v>
       </c>
       <c r="C359" s="2" t="n">
@@ -6144,7 +6135,7 @@
       <c r="A360" s="1" t="n">
         <v>353205</v>
       </c>
-      <c r="B360" s="0" t="s">
+      <c r="B360" s="1" t="s">
         <v>361</v>
       </c>
       <c r="C360" s="2" t="n">
@@ -6155,7 +6146,7 @@
       <c r="A361" s="1" t="n">
         <v>353210</v>
       </c>
-      <c r="B361" s="0" t="s">
+      <c r="B361" s="1" t="s">
         <v>362</v>
       </c>
       <c r="C361" s="2" t="n">
@@ -6166,7 +6157,7 @@
       <c r="A362" s="1" t="n">
         <v>353215</v>
       </c>
-      <c r="B362" s="0" t="s">
+      <c r="B362" s="1" t="s">
         <v>363</v>
       </c>
       <c r="C362" s="2" t="n">
@@ -6177,7 +6168,7 @@
       <c r="A363" s="1" t="n">
         <v>353220</v>
       </c>
-      <c r="B363" s="0" t="s">
+      <c r="B363" s="1" t="s">
         <v>364</v>
       </c>
       <c r="C363" s="2" t="n">
@@ -6188,7 +6179,7 @@
       <c r="A364" s="1" t="n">
         <v>353230</v>
       </c>
-      <c r="B364" s="0" t="s">
+      <c r="B364" s="1" t="s">
         <v>365</v>
       </c>
       <c r="C364" s="2" t="n">
@@ -6199,7 +6190,7 @@
       <c r="A365" s="1" t="n">
         <v>353240</v>
       </c>
-      <c r="B365" s="0" t="s">
+      <c r="B365" s="1" t="s">
         <v>366</v>
       </c>
       <c r="C365" s="2" t="n">
@@ -6210,7 +6201,7 @@
       <c r="A366" s="1" t="n">
         <v>353250</v>
       </c>
-      <c r="B366" s="0" t="s">
+      <c r="B366" s="1" t="s">
         <v>367</v>
       </c>
       <c r="C366" s="2" t="n">
@@ -6221,7 +6212,7 @@
       <c r="A367" s="1" t="n">
         <v>353260</v>
       </c>
-      <c r="B367" s="0" t="s">
+      <c r="B367" s="1" t="s">
         <v>368</v>
       </c>
       <c r="C367" s="2" t="n">
@@ -6232,7 +6223,7 @@
       <c r="A368" s="1" t="n">
         <v>353270</v>
       </c>
-      <c r="B368" s="0" t="s">
+      <c r="B368" s="1" t="s">
         <v>369</v>
       </c>
       <c r="C368" s="2" t="n">
@@ -6243,7 +6234,7 @@
       <c r="A369" s="1" t="n">
         <v>353280</v>
       </c>
-      <c r="B369" s="0" t="s">
+      <c r="B369" s="1" t="s">
         <v>370</v>
       </c>
       <c r="C369" s="2" t="n">
@@ -6254,7 +6245,7 @@
       <c r="A370" s="1" t="n">
         <v>353282</v>
       </c>
-      <c r="B370" s="0" t="s">
+      <c r="B370" s="1" t="s">
         <v>371</v>
       </c>
       <c r="C370" s="2" t="n">
@@ -6265,7 +6256,7 @@
       <c r="A371" s="1" t="n">
         <v>353284</v>
       </c>
-      <c r="B371" s="0" t="s">
+      <c r="B371" s="1" t="s">
         <v>372</v>
       </c>
       <c r="C371" s="2" t="n">
@@ -6276,7 +6267,7 @@
       <c r="A372" s="1" t="n">
         <v>353286</v>
       </c>
-      <c r="B372" s="0" t="s">
+      <c r="B372" s="1" t="s">
         <v>373</v>
       </c>
       <c r="C372" s="2" t="n">
@@ -6287,7 +6278,7 @@
       <c r="A373" s="1" t="n">
         <v>353290</v>
       </c>
-      <c r="B373" s="0" t="s">
+      <c r="B373" s="1" t="s">
         <v>374</v>
       </c>
       <c r="C373" s="2" t="n">
@@ -6298,7 +6289,7 @@
       <c r="A374" s="1" t="n">
         <v>353300</v>
       </c>
-      <c r="B374" s="0" t="s">
+      <c r="B374" s="1" t="s">
         <v>375</v>
       </c>
       <c r="C374" s="2" t="n">
@@ -6309,7 +6300,7 @@
       <c r="A375" s="1" t="n">
         <v>353310</v>
       </c>
-      <c r="B375" s="0" t="s">
+      <c r="B375" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C375" s="2" t="n">
@@ -6320,7 +6311,7 @@
       <c r="A376" s="1" t="n">
         <v>353320</v>
       </c>
-      <c r="B376" s="0" t="s">
+      <c r="B376" s="1" t="s">
         <v>377</v>
       </c>
       <c r="C376" s="2" t="n">
@@ -6331,7 +6322,7 @@
       <c r="A377" s="1" t="n">
         <v>353325</v>
       </c>
-      <c r="B377" s="0" t="s">
+      <c r="B377" s="1" t="s">
         <v>378</v>
       </c>
       <c r="C377" s="2" t="n">
@@ -6342,7 +6333,7 @@
       <c r="A378" s="1" t="n">
         <v>353330</v>
       </c>
-      <c r="B378" s="0" t="s">
+      <c r="B378" s="1" t="s">
         <v>379</v>
       </c>
       <c r="C378" s="2" t="n">
@@ -6353,7 +6344,7 @@
       <c r="A379" s="1" t="n">
         <v>353340</v>
       </c>
-      <c r="B379" s="0" t="s">
+      <c r="B379" s="1" t="s">
         <v>380</v>
       </c>
       <c r="C379" s="2" t="n">
@@ -6364,7 +6355,7 @@
       <c r="A380" s="1" t="n">
         <v>353350</v>
       </c>
-      <c r="B380" s="0" t="s">
+      <c r="B380" s="1" t="s">
         <v>381</v>
       </c>
       <c r="C380" s="2" t="n">
@@ -6375,7 +6366,7 @@
       <c r="A381" s="1" t="n">
         <v>353360</v>
       </c>
-      <c r="B381" s="0" t="s">
+      <c r="B381" s="1" t="s">
         <v>382</v>
       </c>
       <c r="C381" s="2" t="n">
@@ -6386,7 +6377,7 @@
       <c r="A382" s="1" t="n">
         <v>353370</v>
       </c>
-      <c r="B382" s="0" t="s">
+      <c r="B382" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C382" s="2" t="n">
@@ -6397,7 +6388,7 @@
       <c r="A383" s="1" t="n">
         <v>353380</v>
       </c>
-      <c r="B383" s="0" t="s">
+      <c r="B383" s="1" t="s">
         <v>384</v>
       </c>
       <c r="C383" s="2" t="n">
@@ -6408,7 +6399,7 @@
       <c r="A384" s="1" t="n">
         <v>353390</v>
       </c>
-      <c r="B384" s="0" t="s">
+      <c r="B384" s="1" t="s">
         <v>385</v>
       </c>
       <c r="C384" s="2" t="n">
@@ -6419,7 +6410,7 @@
       <c r="A385" s="1" t="n">
         <v>353400</v>
       </c>
-      <c r="B385" s="0" t="s">
+      <c r="B385" s="1" t="s">
         <v>386</v>
       </c>
       <c r="C385" s="2" t="n">
@@ -6430,7 +6421,7 @@
       <c r="A386" s="1" t="n">
         <v>353410</v>
       </c>
-      <c r="B386" s="0" t="s">
+      <c r="B386" s="1" t="s">
         <v>387</v>
       </c>
       <c r="C386" s="2" t="n">
@@ -6441,7 +6432,7 @@
       <c r="A387" s="1" t="n">
         <v>353420</v>
       </c>
-      <c r="B387" s="0" t="s">
+      <c r="B387" s="1" t="s">
         <v>388</v>
       </c>
       <c r="C387" s="2" t="n">
@@ -6452,7 +6443,7 @@
       <c r="A388" s="1" t="n">
         <v>353430</v>
       </c>
-      <c r="B388" s="0" t="s">
+      <c r="B388" s="1" t="s">
         <v>389</v>
       </c>
       <c r="C388" s="2" t="n">
@@ -6463,7 +6454,7 @@
       <c r="A389" s="1" t="n">
         <v>353440</v>
       </c>
-      <c r="B389" s="0" t="s">
+      <c r="B389" s="1" t="s">
         <v>390</v>
       </c>
       <c r="C389" s="2" t="n">
@@ -6474,7 +6465,7 @@
       <c r="A390" s="1" t="n">
         <v>353450</v>
       </c>
-      <c r="B390" s="0" t="s">
+      <c r="B390" s="1" t="s">
         <v>391</v>
       </c>
       <c r="C390" s="2" t="n">
@@ -6485,7 +6476,7 @@
       <c r="A391" s="1" t="n">
         <v>353460</v>
       </c>
-      <c r="B391" s="0" t="s">
+      <c r="B391" s="1" t="s">
         <v>392</v>
       </c>
       <c r="C391" s="2" t="n">
@@ -6496,7 +6487,7 @@
       <c r="A392" s="1" t="n">
         <v>353470</v>
       </c>
-      <c r="B392" s="0" t="s">
+      <c r="B392" s="1" t="s">
         <v>393</v>
       </c>
       <c r="C392" s="2" t="n">
@@ -6507,7 +6498,7 @@
       <c r="A393" s="1" t="n">
         <v>353475</v>
       </c>
-      <c r="B393" s="0" t="s">
+      <c r="B393" s="1" t="s">
         <v>394</v>
       </c>
       <c r="C393" s="2" t="n">
@@ -6518,7 +6509,7 @@
       <c r="A394" s="1" t="n">
         <v>353480</v>
       </c>
-      <c r="B394" s="0" t="s">
+      <c r="B394" s="1" t="s">
         <v>395</v>
       </c>
       <c r="C394" s="2" t="n">
@@ -6529,7 +6520,7 @@
       <c r="A395" s="1" t="n">
         <v>353490</v>
       </c>
-      <c r="B395" s="0" t="s">
+      <c r="B395" s="1" t="s">
         <v>396</v>
       </c>
       <c r="C395" s="2" t="n">
@@ -6540,7 +6531,7 @@
       <c r="A396" s="1" t="n">
         <v>353500</v>
       </c>
-      <c r="B396" s="0" t="s">
+      <c r="B396" s="1" t="s">
         <v>397</v>
       </c>
       <c r="C396" s="2" t="n">
@@ -6551,7 +6542,7 @@
       <c r="A397" s="1" t="n">
         <v>353510</v>
       </c>
-      <c r="B397" s="0" t="s">
+      <c r="B397" s="1" t="s">
         <v>398</v>
       </c>
       <c r="C397" s="2" t="n">
@@ -6562,7 +6553,7 @@
       <c r="A398" s="1" t="n">
         <v>353520</v>
       </c>
-      <c r="B398" s="0" t="s">
+      <c r="B398" s="1" t="s">
         <v>399</v>
       </c>
       <c r="C398" s="2" t="n">
@@ -6573,7 +6564,7 @@
       <c r="A399" s="1" t="n">
         <v>353530</v>
       </c>
-      <c r="B399" s="0" t="s">
+      <c r="B399" s="1" t="s">
         <v>400</v>
       </c>
       <c r="C399" s="2" t="n">
@@ -6584,7 +6575,7 @@
       <c r="A400" s="1" t="n">
         <v>353540</v>
       </c>
-      <c r="B400" s="0" t="s">
+      <c r="B400" s="1" t="s">
         <v>401</v>
       </c>
       <c r="C400" s="2" t="n">
@@ -6595,7 +6586,7 @@
       <c r="A401" s="1" t="n">
         <v>353550</v>
       </c>
-      <c r="B401" s="0" t="s">
+      <c r="B401" s="1" t="s">
         <v>402</v>
       </c>
       <c r="C401" s="2" t="n">
@@ -6606,7 +6597,7 @@
       <c r="A402" s="1" t="n">
         <v>353560</v>
       </c>
-      <c r="B402" s="0" t="s">
+      <c r="B402" s="1" t="s">
         <v>403</v>
       </c>
       <c r="C402" s="2" t="n">
@@ -6617,7 +6608,7 @@
       <c r="A403" s="1" t="n">
         <v>353570</v>
       </c>
-      <c r="B403" s="0" t="s">
+      <c r="B403" s="1" t="s">
         <v>404</v>
       </c>
       <c r="C403" s="2" t="n">
@@ -6628,7 +6619,7 @@
       <c r="A404" s="1" t="n">
         <v>353580</v>
       </c>
-      <c r="B404" s="0" t="s">
+      <c r="B404" s="1" t="s">
         <v>405</v>
       </c>
       <c r="C404" s="2" t="n">
@@ -6639,7 +6630,7 @@
       <c r="A405" s="1" t="n">
         <v>353590</v>
       </c>
-      <c r="B405" s="0" t="s">
+      <c r="B405" s="1" t="s">
         <v>406</v>
       </c>
       <c r="C405" s="2" t="n">
@@ -6650,7 +6641,7 @@
       <c r="A406" s="1" t="n">
         <v>353600</v>
       </c>
-      <c r="B406" s="0" t="s">
+      <c r="B406" s="1" t="s">
         <v>407</v>
       </c>
       <c r="C406" s="2" t="n">
@@ -6661,7 +6652,7 @@
       <c r="A407" s="1" t="n">
         <v>353610</v>
       </c>
-      <c r="B407" s="0" t="s">
+      <c r="B407" s="1" t="s">
         <v>408</v>
       </c>
       <c r="C407" s="2" t="n">
@@ -6672,7 +6663,7 @@
       <c r="A408" s="1" t="n">
         <v>353620</v>
       </c>
-      <c r="B408" s="0" t="s">
+      <c r="B408" s="1" t="s">
         <v>409</v>
       </c>
       <c r="C408" s="2" t="n">
@@ -6683,7 +6674,7 @@
       <c r="A409" s="1" t="n">
         <v>353625</v>
       </c>
-      <c r="B409" s="0" t="s">
+      <c r="B409" s="1" t="s">
         <v>410</v>
       </c>
       <c r="C409" s="2" t="n">
@@ -6694,7 +6685,7 @@
       <c r="A410" s="1" t="n">
         <v>353630</v>
       </c>
-      <c r="B410" s="0" t="s">
+      <c r="B410" s="1" t="s">
         <v>411</v>
       </c>
       <c r="C410" s="2" t="n">
@@ -6705,7 +6696,7 @@
       <c r="A411" s="1" t="n">
         <v>353640</v>
       </c>
-      <c r="B411" s="0" t="s">
+      <c r="B411" s="1" t="s">
         <v>412</v>
       </c>
       <c r="C411" s="2" t="n">
@@ -6716,7 +6707,7 @@
       <c r="A412" s="1" t="n">
         <v>353650</v>
       </c>
-      <c r="B412" s="0" t="s">
+      <c r="B412" s="1" t="s">
         <v>413</v>
       </c>
       <c r="C412" s="2" t="n">
@@ -6727,7 +6718,7 @@
       <c r="A413" s="1" t="n">
         <v>353657</v>
       </c>
-      <c r="B413" s="0" t="s">
+      <c r="B413" s="1" t="s">
         <v>414</v>
       </c>
       <c r="C413" s="2" t="n">
@@ -6738,7 +6729,7 @@
       <c r="A414" s="1" t="n">
         <v>353660</v>
       </c>
-      <c r="B414" s="0" t="s">
+      <c r="B414" s="1" t="s">
         <v>415</v>
       </c>
       <c r="C414" s="2" t="n">
@@ -6749,7 +6740,7 @@
       <c r="A415" s="1" t="n">
         <v>353670</v>
       </c>
-      <c r="B415" s="0" t="s">
+      <c r="B415" s="1" t="s">
         <v>416</v>
       </c>
       <c r="C415" s="2" t="n">
@@ -6760,7 +6751,7 @@
       <c r="A416" s="1" t="n">
         <v>353680</v>
       </c>
-      <c r="B416" s="0" t="s">
+      <c r="B416" s="1" t="s">
         <v>417</v>
       </c>
       <c r="C416" s="2" t="n">
@@ -6771,7 +6762,7 @@
       <c r="A417" s="1" t="n">
         <v>353690</v>
       </c>
-      <c r="B417" s="0" t="s">
+      <c r="B417" s="1" t="s">
         <v>418</v>
       </c>
       <c r="C417" s="2" t="n">
@@ -6782,7 +6773,7 @@
       <c r="A418" s="1" t="n">
         <v>353700</v>
       </c>
-      <c r="B418" s="0" t="s">
+      <c r="B418" s="1" t="s">
         <v>419</v>
       </c>
       <c r="C418" s="2" t="n">
@@ -6793,7 +6784,7 @@
       <c r="A419" s="1" t="n">
         <v>353710</v>
       </c>
-      <c r="B419" s="0" t="s">
+      <c r="B419" s="1" t="s">
         <v>420</v>
       </c>
       <c r="C419" s="2" t="n">
@@ -6804,7 +6795,7 @@
       <c r="A420" s="1" t="n">
         <v>353715</v>
       </c>
-      <c r="B420" s="0" t="s">
+      <c r="B420" s="1" t="s">
         <v>421</v>
       </c>
       <c r="C420" s="2" t="n">
@@ -6815,7 +6806,7 @@
       <c r="A421" s="1" t="n">
         <v>353720</v>
       </c>
-      <c r="B421" s="0" t="s">
+      <c r="B421" s="1" t="s">
         <v>422</v>
       </c>
       <c r="C421" s="2" t="n">
@@ -6826,7 +6817,7 @@
       <c r="A422" s="1" t="n">
         <v>353730</v>
       </c>
-      <c r="B422" s="0" t="s">
+      <c r="B422" s="1" t="s">
         <v>423</v>
       </c>
       <c r="C422" s="2" t="n">
@@ -6837,7 +6828,7 @@
       <c r="A423" s="1" t="n">
         <v>353740</v>
       </c>
-      <c r="B423" s="0" t="s">
+      <c r="B423" s="1" t="s">
         <v>424</v>
       </c>
       <c r="C423" s="2" t="n">
@@ -6848,7 +6839,7 @@
       <c r="A424" s="1" t="n">
         <v>353750</v>
       </c>
-      <c r="B424" s="0" t="s">
+      <c r="B424" s="1" t="s">
         <v>425</v>
       </c>
       <c r="C424" s="2" t="n">
@@ -6859,7 +6850,7 @@
       <c r="A425" s="1" t="n">
         <v>353760</v>
       </c>
-      <c r="B425" s="0" t="s">
+      <c r="B425" s="1" t="s">
         <v>426</v>
       </c>
       <c r="C425" s="2" t="n">
@@ -6870,7 +6861,7 @@
       <c r="A426" s="1" t="n">
         <v>353770</v>
       </c>
-      <c r="B426" s="0" t="s">
+      <c r="B426" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C426" s="2" t="n">
@@ -6881,7 +6872,7 @@
       <c r="A427" s="1" t="n">
         <v>353780</v>
       </c>
-      <c r="B427" s="0" t="s">
+      <c r="B427" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C427" s="2" t="n">
@@ -6892,7 +6883,7 @@
       <c r="A428" s="1" t="n">
         <v>353790</v>
       </c>
-      <c r="B428" s="0" t="s">
+      <c r="B428" s="1" t="s">
         <v>429</v>
       </c>
       <c r="C428" s="2" t="n">
@@ -6903,7 +6894,7 @@
       <c r="A429" s="1" t="n">
         <v>353800</v>
       </c>
-      <c r="B429" s="0" t="s">
+      <c r="B429" s="1" t="s">
         <v>430</v>
       </c>
       <c r="C429" s="2" t="n">
@@ -6914,7 +6905,7 @@
       <c r="A430" s="1" t="n">
         <v>353810</v>
       </c>
-      <c r="B430" s="0" t="s">
+      <c r="B430" s="1" t="s">
         <v>431</v>
       </c>
       <c r="C430" s="2" t="n">
@@ -6925,7 +6916,7 @@
       <c r="A431" s="1" t="n">
         <v>353820</v>
       </c>
-      <c r="B431" s="0" t="s">
+      <c r="B431" s="1" t="s">
         <v>432</v>
       </c>
       <c r="C431" s="2" t="n">
@@ -6936,7 +6927,7 @@
       <c r="A432" s="1" t="n">
         <v>353830</v>
       </c>
-      <c r="B432" s="0" t="s">
+      <c r="B432" s="1" t="s">
         <v>433</v>
       </c>
       <c r="C432" s="2" t="n">
@@ -6947,7 +6938,7 @@
       <c r="A433" s="1" t="n">
         <v>353850</v>
       </c>
-      <c r="B433" s="0" t="s">
+      <c r="B433" s="1" t="s">
         <v>434</v>
       </c>
       <c r="C433" s="2" t="n">
@@ -6958,7 +6949,7 @@
       <c r="A434" s="1" t="n">
         <v>353860</v>
       </c>
-      <c r="B434" s="0" t="s">
+      <c r="B434" s="1" t="s">
         <v>435</v>
       </c>
       <c r="C434" s="2" t="n">
@@ -6969,7 +6960,7 @@
       <c r="A435" s="1" t="n">
         <v>353870</v>
       </c>
-      <c r="B435" s="0" t="s">
+      <c r="B435" s="1" t="s">
         <v>436</v>
       </c>
       <c r="C435" s="2" t="n">
@@ -6980,7 +6971,7 @@
       <c r="A436" s="1" t="n">
         <v>353880</v>
       </c>
-      <c r="B436" s="0" t="s">
+      <c r="B436" s="1" t="s">
         <v>437</v>
       </c>
       <c r="C436" s="2" t="n">
@@ -6991,7 +6982,7 @@
       <c r="A437" s="1" t="n">
         <v>353890</v>
       </c>
-      <c r="B437" s="0" t="s">
+      <c r="B437" s="1" t="s">
         <v>438</v>
       </c>
       <c r="C437" s="2" t="n">
@@ -7002,7 +6993,7 @@
       <c r="A438" s="1" t="n">
         <v>353900</v>
       </c>
-      <c r="B438" s="0" t="s">
+      <c r="B438" s="1" t="s">
         <v>439</v>
       </c>
       <c r="C438" s="2" t="n">
@@ -7013,7 +7004,7 @@
       <c r="A439" s="1" t="n">
         <v>353910</v>
       </c>
-      <c r="B439" s="0" t="s">
+      <c r="B439" s="1" t="s">
         <v>440</v>
       </c>
       <c r="C439" s="2" t="n">
@@ -7024,7 +7015,7 @@
       <c r="A440" s="1" t="n">
         <v>353920</v>
       </c>
-      <c r="B440" s="0" t="s">
+      <c r="B440" s="1" t="s">
         <v>441</v>
       </c>
       <c r="C440" s="2" t="n">
@@ -7035,7 +7026,7 @@
       <c r="A441" s="1" t="n">
         <v>353930</v>
       </c>
-      <c r="B441" s="0" t="s">
+      <c r="B441" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C441" s="2" t="n">
@@ -7046,7 +7037,7 @@
       <c r="A442" s="1" t="n">
         <v>353940</v>
       </c>
-      <c r="B442" s="0" t="s">
+      <c r="B442" s="1" t="s">
         <v>443</v>
       </c>
       <c r="C442" s="2" t="n">
@@ -7057,7 +7048,7 @@
       <c r="A443" s="1" t="n">
         <v>353950</v>
       </c>
-      <c r="B443" s="0" t="s">
+      <c r="B443" s="1" t="s">
         <v>444</v>
       </c>
       <c r="C443" s="2" t="n">
@@ -7068,7 +7059,7 @@
       <c r="A444" s="1" t="n">
         <v>353960</v>
       </c>
-      <c r="B444" s="0" t="s">
+      <c r="B444" s="1" t="s">
         <v>445</v>
       </c>
       <c r="C444" s="2" t="n">
@@ -7079,7 +7070,7 @@
       <c r="A445" s="1" t="n">
         <v>353970</v>
       </c>
-      <c r="B445" s="0" t="s">
+      <c r="B445" s="1" t="s">
         <v>446</v>
       </c>
       <c r="C445" s="2" t="n">
@@ -7090,7 +7081,7 @@
       <c r="A446" s="1" t="n">
         <v>353980</v>
       </c>
-      <c r="B446" s="0" t="s">
+      <c r="B446" s="1" t="s">
         <v>447</v>
       </c>
       <c r="C446" s="2" t="n">
@@ -7101,7 +7092,7 @@
       <c r="A447" s="1" t="n">
         <v>353990</v>
       </c>
-      <c r="B447" s="0" t="s">
+      <c r="B447" s="1" t="s">
         <v>448</v>
       </c>
       <c r="C447" s="2" t="n">
@@ -7112,7 +7103,7 @@
       <c r="A448" s="1" t="n">
         <v>354000</v>
       </c>
-      <c r="B448" s="0" t="s">
+      <c r="B448" s="1" t="s">
         <v>449</v>
       </c>
       <c r="C448" s="2" t="n">
@@ -7123,7 +7114,7 @@
       <c r="A449" s="1" t="n">
         <v>354010</v>
       </c>
-      <c r="B449" s="0" t="s">
+      <c r="B449" s="1" t="s">
         <v>450</v>
       </c>
       <c r="C449" s="2" t="n">
@@ -7134,7 +7125,7 @@
       <c r="A450" s="1" t="n">
         <v>354020</v>
       </c>
-      <c r="B450" s="0" t="s">
+      <c r="B450" s="1" t="s">
         <v>451</v>
       </c>
       <c r="C450" s="2" t="n">
@@ -7145,7 +7136,7 @@
       <c r="A451" s="1" t="n">
         <v>354025</v>
       </c>
-      <c r="B451" s="0" t="s">
+      <c r="B451" s="1" t="s">
         <v>452</v>
       </c>
       <c r="C451" s="2" t="n">
@@ -7156,7 +7147,7 @@
       <c r="A452" s="1" t="n">
         <v>354030</v>
       </c>
-      <c r="B452" s="0" t="s">
+      <c r="B452" s="1" t="s">
         <v>453</v>
       </c>
       <c r="C452" s="2" t="n">
@@ -7167,7 +7158,7 @@
       <c r="A453" s="1" t="n">
         <v>354040</v>
       </c>
-      <c r="B453" s="0" t="s">
+      <c r="B453" s="1" t="s">
         <v>454</v>
       </c>
       <c r="C453" s="2" t="n">
@@ -7178,7 +7169,7 @@
       <c r="A454" s="1" t="n">
         <v>354050</v>
       </c>
-      <c r="B454" s="0" t="s">
+      <c r="B454" s="1" t="s">
         <v>455</v>
       </c>
       <c r="C454" s="2" t="n">
@@ -7189,7 +7180,7 @@
       <c r="A455" s="1" t="n">
         <v>354060</v>
       </c>
-      <c r="B455" s="0" t="s">
+      <c r="B455" s="1" t="s">
         <v>456</v>
       </c>
       <c r="C455" s="2" t="n">
@@ -7200,7 +7191,7 @@
       <c r="A456" s="1" t="n">
         <v>354070</v>
       </c>
-      <c r="B456" s="0" t="s">
+      <c r="B456" s="1" t="s">
         <v>457</v>
       </c>
       <c r="C456" s="2" t="n">
@@ -7211,7 +7202,7 @@
       <c r="A457" s="1" t="n">
         <v>354075</v>
       </c>
-      <c r="B457" s="0" t="s">
+      <c r="B457" s="1" t="s">
         <v>458</v>
       </c>
       <c r="C457" s="2" t="n">
@@ -7222,7 +7213,7 @@
       <c r="A458" s="1" t="n">
         <v>354080</v>
       </c>
-      <c r="B458" s="0" t="s">
+      <c r="B458" s="1" t="s">
         <v>459</v>
       </c>
       <c r="C458" s="2" t="n">
@@ -7233,7 +7224,7 @@
       <c r="A459" s="1" t="n">
         <v>354085</v>
       </c>
-      <c r="B459" s="0" t="s">
+      <c r="B459" s="1" t="s">
         <v>460</v>
       </c>
       <c r="C459" s="2" t="n">
@@ -7244,7 +7235,7 @@
       <c r="A460" s="1" t="n">
         <v>354090</v>
       </c>
-      <c r="B460" s="0" t="s">
+      <c r="B460" s="1" t="s">
         <v>461</v>
       </c>
       <c r="C460" s="2" t="n">
@@ -7255,7 +7246,7 @@
       <c r="A461" s="1" t="n">
         <v>354100</v>
       </c>
-      <c r="B461" s="0" t="s">
+      <c r="B461" s="1" t="s">
         <v>462</v>
       </c>
       <c r="C461" s="2" t="n">
@@ -7266,7 +7257,7 @@
       <c r="A462" s="1" t="n">
         <v>354105</v>
       </c>
-      <c r="B462" s="0" t="s">
+      <c r="B462" s="1" t="s">
         <v>463</v>
       </c>
       <c r="C462" s="2" t="n">
@@ -7277,7 +7268,7 @@
       <c r="A463" s="1" t="n">
         <v>354110</v>
       </c>
-      <c r="B463" s="0" t="s">
+      <c r="B463" s="1" t="s">
         <v>464</v>
       </c>
       <c r="C463" s="2" t="n">
@@ -7288,7 +7279,7 @@
       <c r="A464" s="1" t="n">
         <v>354120</v>
       </c>
-      <c r="B464" s="0" t="s">
+      <c r="B464" s="1" t="s">
         <v>465</v>
       </c>
       <c r="C464" s="2" t="n">
@@ -7299,7 +7290,7 @@
       <c r="A465" s="1" t="n">
         <v>354130</v>
       </c>
-      <c r="B465" s="0" t="s">
+      <c r="B465" s="1" t="s">
         <v>466</v>
       </c>
       <c r="C465" s="2" t="n">
@@ -7310,7 +7301,7 @@
       <c r="A466" s="1" t="n">
         <v>354140</v>
       </c>
-      <c r="B466" s="0" t="s">
+      <c r="B466" s="1" t="s">
         <v>467</v>
       </c>
       <c r="C466" s="2" t="n">
@@ -7321,7 +7312,7 @@
       <c r="A467" s="1" t="n">
         <v>354150</v>
       </c>
-      <c r="B467" s="0" t="s">
+      <c r="B467" s="1" t="s">
         <v>468</v>
       </c>
       <c r="C467" s="2" t="n">
@@ -7332,7 +7323,7 @@
       <c r="A468" s="1" t="n">
         <v>354160</v>
       </c>
-      <c r="B468" s="0" t="s">
+      <c r="B468" s="1" t="s">
         <v>469</v>
       </c>
       <c r="C468" s="2" t="n">
@@ -7343,7 +7334,7 @@
       <c r="A469" s="1" t="n">
         <v>354165</v>
       </c>
-      <c r="B469" s="0" t="s">
+      <c r="B469" s="1" t="s">
         <v>470</v>
       </c>
       <c r="C469" s="2" t="n">
@@ -7354,7 +7345,7 @@
       <c r="A470" s="1" t="n">
         <v>354170</v>
       </c>
-      <c r="B470" s="0" t="s">
+      <c r="B470" s="1" t="s">
         <v>471</v>
       </c>
       <c r="C470" s="2" t="n">
@@ -7365,7 +7356,7 @@
       <c r="A471" s="1" t="n">
         <v>354180</v>
       </c>
-      <c r="B471" s="0" t="s">
+      <c r="B471" s="1" t="s">
         <v>472</v>
       </c>
       <c r="C471" s="2" t="n">
@@ -7376,7 +7367,7 @@
       <c r="A472" s="1" t="n">
         <v>354190</v>
       </c>
-      <c r="B472" s="0" t="s">
+      <c r="B472" s="1" t="s">
         <v>473</v>
       </c>
       <c r="C472" s="2" t="n">
@@ -7387,7 +7378,7 @@
       <c r="A473" s="1" t="n">
         <v>354200</v>
       </c>
-      <c r="B473" s="0" t="s">
+      <c r="B473" s="1" t="s">
         <v>474</v>
       </c>
       <c r="C473" s="2" t="n">
@@ -7398,7 +7389,7 @@
       <c r="A474" s="1" t="n">
         <v>354210</v>
       </c>
-      <c r="B474" s="0" t="s">
+      <c r="B474" s="1" t="s">
         <v>475</v>
       </c>
       <c r="C474" s="2" t="n">
@@ -7409,7 +7400,7 @@
       <c r="A475" s="1" t="n">
         <v>354220</v>
       </c>
-      <c r="B475" s="0" t="s">
+      <c r="B475" s="1" t="s">
         <v>476</v>
       </c>
       <c r="C475" s="2" t="n">
@@ -7420,7 +7411,7 @@
       <c r="A476" s="1" t="n">
         <v>354230</v>
       </c>
-      <c r="B476" s="0" t="s">
+      <c r="B476" s="1" t="s">
         <v>477</v>
       </c>
       <c r="C476" s="2" t="n">
@@ -7431,7 +7422,7 @@
       <c r="A477" s="1" t="n">
         <v>354240</v>
       </c>
-      <c r="B477" s="0" t="s">
+      <c r="B477" s="1" t="s">
         <v>478</v>
       </c>
       <c r="C477" s="2" t="n">
@@ -7442,7 +7433,7 @@
       <c r="A478" s="1" t="n">
         <v>354250</v>
       </c>
-      <c r="B478" s="0" t="s">
+      <c r="B478" s="1" t="s">
         <v>479</v>
       </c>
       <c r="C478" s="2" t="n">
@@ -7453,7 +7444,7 @@
       <c r="A479" s="1" t="n">
         <v>354260</v>
       </c>
-      <c r="B479" s="0" t="s">
+      <c r="B479" s="1" t="s">
         <v>480</v>
       </c>
       <c r="C479" s="2" t="n">
@@ -7464,7 +7455,7 @@
       <c r="A480" s="1" t="n">
         <v>354270</v>
       </c>
-      <c r="B480" s="0" t="s">
+      <c r="B480" s="1" t="s">
         <v>481</v>
       </c>
       <c r="C480" s="2" t="n">
@@ -7475,7 +7466,7 @@
       <c r="A481" s="1" t="n">
         <v>354280</v>
       </c>
-      <c r="B481" s="0" t="s">
+      <c r="B481" s="1" t="s">
         <v>482</v>
       </c>
       <c r="C481" s="2" t="n">
@@ -7486,7 +7477,7 @@
       <c r="A482" s="1" t="n">
         <v>354290</v>
       </c>
-      <c r="B482" s="0" t="s">
+      <c r="B482" s="1" t="s">
         <v>483</v>
       </c>
       <c r="C482" s="2" t="n">
@@ -7497,7 +7488,7 @@
       <c r="A483" s="1" t="n">
         <v>354300</v>
       </c>
-      <c r="B483" s="0" t="s">
+      <c r="B483" s="1" t="s">
         <v>484</v>
       </c>
       <c r="C483" s="2" t="n">
@@ -7508,7 +7499,7 @@
       <c r="A484" s="1" t="n">
         <v>354310</v>
       </c>
-      <c r="B484" s="0" t="s">
+      <c r="B484" s="1" t="s">
         <v>485</v>
       </c>
       <c r="C484" s="2" t="n">
@@ -7519,7 +7510,7 @@
       <c r="A485" s="1" t="n">
         <v>354320</v>
       </c>
-      <c r="B485" s="0" t="s">
+      <c r="B485" s="1" t="s">
         <v>486</v>
       </c>
       <c r="C485" s="2" t="n">
@@ -7530,7 +7521,7 @@
       <c r="A486" s="1" t="n">
         <v>354323</v>
       </c>
-      <c r="B486" s="0" t="s">
+      <c r="B486" s="1" t="s">
         <v>487</v>
       </c>
       <c r="C486" s="2" t="n">
@@ -7541,7 +7532,7 @@
       <c r="A487" s="1" t="n">
         <v>354325</v>
       </c>
-      <c r="B487" s="0" t="s">
+      <c r="B487" s="1" t="s">
         <v>488</v>
       </c>
       <c r="C487" s="2" t="n">
@@ -7552,7 +7543,7 @@
       <c r="A488" s="1" t="n">
         <v>354330</v>
       </c>
-      <c r="B488" s="0" t="s">
+      <c r="B488" s="1" t="s">
         <v>489</v>
       </c>
       <c r="C488" s="2" t="n">
@@ -7563,7 +7554,7 @@
       <c r="A489" s="1" t="n">
         <v>354340</v>
       </c>
-      <c r="B489" s="0" t="s">
+      <c r="B489" s="1" t="s">
         <v>490</v>
       </c>
       <c r="C489" s="2" t="n">
@@ -7574,7 +7565,7 @@
       <c r="A490" s="1" t="n">
         <v>354350</v>
       </c>
-      <c r="B490" s="0" t="s">
+      <c r="B490" s="1" t="s">
         <v>491</v>
       </c>
       <c r="C490" s="2" t="n">
@@ -7585,7 +7576,7 @@
       <c r="A491" s="1" t="n">
         <v>354360</v>
       </c>
-      <c r="B491" s="0" t="s">
+      <c r="B491" s="1" t="s">
         <v>492</v>
       </c>
       <c r="C491" s="2" t="n">
@@ -7596,7 +7587,7 @@
       <c r="A492" s="1" t="n">
         <v>354370</v>
       </c>
-      <c r="B492" s="0" t="s">
+      <c r="B492" s="1" t="s">
         <v>493</v>
       </c>
       <c r="C492" s="2" t="n">
@@ -7607,7 +7598,7 @@
       <c r="A493" s="1" t="n">
         <v>354380</v>
       </c>
-      <c r="B493" s="0" t="s">
+      <c r="B493" s="1" t="s">
         <v>494</v>
       </c>
       <c r="C493" s="2" t="n">
@@ -7618,7 +7609,7 @@
       <c r="A494" s="1" t="n">
         <v>354390</v>
       </c>
-      <c r="B494" s="0" t="s">
+      <c r="B494" s="1" t="s">
         <v>495</v>
       </c>
       <c r="C494" s="2" t="n">
@@ -7629,7 +7620,7 @@
       <c r="A495" s="1" t="n">
         <v>354400</v>
       </c>
-      <c r="B495" s="0" t="s">
+      <c r="B495" s="1" t="s">
         <v>496</v>
       </c>
       <c r="C495" s="2" t="n">
@@ -7640,7 +7631,7 @@
       <c r="A496" s="1" t="n">
         <v>354410</v>
       </c>
-      <c r="B496" s="0" t="s">
+      <c r="B496" s="1" t="s">
         <v>497</v>
       </c>
       <c r="C496" s="2" t="n">
@@ -7651,7 +7642,7 @@
       <c r="A497" s="1" t="n">
         <v>354420</v>
       </c>
-      <c r="B497" s="0" t="s">
+      <c r="B497" s="1" t="s">
         <v>498</v>
       </c>
       <c r="C497" s="2" t="n">
@@ -7662,7 +7653,7 @@
       <c r="A498" s="1" t="n">
         <v>354425</v>
       </c>
-      <c r="B498" s="0" t="s">
+      <c r="B498" s="1" t="s">
         <v>499</v>
       </c>
       <c r="C498" s="2" t="n">
@@ -7673,7 +7664,7 @@
       <c r="A499" s="1" t="n">
         <v>354430</v>
       </c>
-      <c r="B499" s="0" t="s">
+      <c r="B499" s="1" t="s">
         <v>500</v>
       </c>
       <c r="C499" s="2" t="n">
@@ -7684,7 +7675,7 @@
       <c r="A500" s="1" t="n">
         <v>354440</v>
       </c>
-      <c r="B500" s="0" t="s">
+      <c r="B500" s="1" t="s">
         <v>501</v>
       </c>
       <c r="C500" s="2" t="n">
@@ -7695,7 +7686,7 @@
       <c r="A501" s="1" t="n">
         <v>354450</v>
       </c>
-      <c r="B501" s="0" t="s">
+      <c r="B501" s="1" t="s">
         <v>502</v>
       </c>
       <c r="C501" s="2" t="n">
@@ -7706,7 +7697,7 @@
       <c r="A502" s="1" t="n">
         <v>354460</v>
       </c>
-      <c r="B502" s="0" t="s">
+      <c r="B502" s="1" t="s">
         <v>503</v>
       </c>
       <c r="C502" s="2" t="n">
@@ -7717,7 +7708,7 @@
       <c r="A503" s="1" t="n">
         <v>354470</v>
       </c>
-      <c r="B503" s="0" t="s">
+      <c r="B503" s="1" t="s">
         <v>504</v>
       </c>
       <c r="C503" s="2" t="n">
@@ -7728,7 +7719,7 @@
       <c r="A504" s="1" t="n">
         <v>354480</v>
       </c>
-      <c r="B504" s="0" t="s">
+      <c r="B504" s="1" t="s">
         <v>505</v>
       </c>
       <c r="C504" s="2" t="n">
@@ -7739,7 +7730,7 @@
       <c r="A505" s="1" t="n">
         <v>354490</v>
       </c>
-      <c r="B505" s="0" t="s">
+      <c r="B505" s="1" t="s">
         <v>506</v>
       </c>
       <c r="C505" s="2" t="n">
@@ -7750,7 +7741,7 @@
       <c r="A506" s="1" t="n">
         <v>354500</v>
       </c>
-      <c r="B506" s="0" t="s">
+      <c r="B506" s="1" t="s">
         <v>507</v>
       </c>
       <c r="C506" s="2" t="n">
@@ -7761,7 +7752,7 @@
       <c r="A507" s="1" t="n">
         <v>354510</v>
       </c>
-      <c r="B507" s="0" t="s">
+      <c r="B507" s="1" t="s">
         <v>508</v>
       </c>
       <c r="C507" s="2" t="n">
@@ -7772,7 +7763,7 @@
       <c r="A508" s="1" t="n">
         <v>354515</v>
       </c>
-      <c r="B508" s="0" t="s">
+      <c r="B508" s="1" t="s">
         <v>509</v>
       </c>
       <c r="C508" s="2" t="n">
@@ -7783,7 +7774,7 @@
       <c r="A509" s="1" t="n">
         <v>354520</v>
       </c>
-      <c r="B509" s="0" t="s">
+      <c r="B509" s="1" t="s">
         <v>510</v>
       </c>
       <c r="C509" s="2" t="n">
@@ -7794,7 +7785,7 @@
       <c r="A510" s="1" t="n">
         <v>354530</v>
       </c>
-      <c r="B510" s="0" t="s">
+      <c r="B510" s="1" t="s">
         <v>511</v>
       </c>
       <c r="C510" s="2" t="n">
@@ -7805,7 +7796,7 @@
       <c r="A511" s="1" t="n">
         <v>354540</v>
       </c>
-      <c r="B511" s="0" t="s">
+      <c r="B511" s="1" t="s">
         <v>512</v>
       </c>
       <c r="C511" s="2" t="n">
@@ -7816,7 +7807,7 @@
       <c r="A512" s="1" t="n">
         <v>354550</v>
       </c>
-      <c r="B512" s="0" t="s">
+      <c r="B512" s="1" t="s">
         <v>513</v>
       </c>
       <c r="C512" s="2" t="n">
@@ -7827,7 +7818,7 @@
       <c r="A513" s="1" t="n">
         <v>354560</v>
       </c>
-      <c r="B513" s="0" t="s">
+      <c r="B513" s="1" t="s">
         <v>514</v>
       </c>
       <c r="C513" s="2" t="n">
@@ -7838,7 +7829,7 @@
       <c r="A514" s="1" t="n">
         <v>354570</v>
       </c>
-      <c r="B514" s="0" t="s">
+      <c r="B514" s="1" t="s">
         <v>515</v>
       </c>
       <c r="C514" s="2" t="n">
@@ -7849,7 +7840,7 @@
       <c r="A515" s="1" t="n">
         <v>354580</v>
       </c>
-      <c r="B515" s="0" t="s">
+      <c r="B515" s="1" t="s">
         <v>516</v>
       </c>
       <c r="C515" s="2" t="n">
@@ -7860,7 +7851,7 @@
       <c r="A516" s="1" t="n">
         <v>354600</v>
       </c>
-      <c r="B516" s="0" t="s">
+      <c r="B516" s="1" t="s">
         <v>517</v>
       </c>
       <c r="C516" s="2" t="n">
@@ -7871,7 +7862,7 @@
       <c r="A517" s="1" t="n">
         <v>354610</v>
       </c>
-      <c r="B517" s="0" t="s">
+      <c r="B517" s="1" t="s">
         <v>518</v>
       </c>
       <c r="C517" s="2" t="n">
@@ -7882,7 +7873,7 @@
       <c r="A518" s="1" t="n">
         <v>354620</v>
       </c>
-      <c r="B518" s="0" t="s">
+      <c r="B518" s="1" t="s">
         <v>519</v>
       </c>
       <c r="C518" s="2" t="n">
@@ -7893,7 +7884,7 @@
       <c r="A519" s="1" t="n">
         <v>354625</v>
       </c>
-      <c r="B519" s="0" t="s">
+      <c r="B519" s="1" t="s">
         <v>520</v>
       </c>
       <c r="C519" s="2" t="n">
@@ -7904,7 +7895,7 @@
       <c r="A520" s="1" t="n">
         <v>354630</v>
       </c>
-      <c r="B520" s="0" t="s">
+      <c r="B520" s="1" t="s">
         <v>521</v>
       </c>
       <c r="C520" s="2" t="n">
@@ -7915,7 +7906,7 @@
       <c r="A521" s="1" t="n">
         <v>354640</v>
       </c>
-      <c r="B521" s="0" t="s">
+      <c r="B521" s="1" t="s">
         <v>522</v>
       </c>
       <c r="C521" s="2" t="n">
@@ -7926,7 +7917,7 @@
       <c r="A522" s="1" t="n">
         <v>354650</v>
       </c>
-      <c r="B522" s="0" t="s">
+      <c r="B522" s="1" t="s">
         <v>523</v>
       </c>
       <c r="C522" s="2" t="n">
@@ -7937,7 +7928,7 @@
       <c r="A523" s="1" t="n">
         <v>354660</v>
       </c>
-      <c r="B523" s="0" t="s">
+      <c r="B523" s="1" t="s">
         <v>524</v>
       </c>
       <c r="C523" s="2" t="n">
@@ -7948,7 +7939,7 @@
       <c r="A524" s="1" t="n">
         <v>354670</v>
       </c>
-      <c r="B524" s="0" t="s">
+      <c r="B524" s="1" t="s">
         <v>525</v>
       </c>
       <c r="C524" s="2" t="n">
@@ -7959,7 +7950,7 @@
       <c r="A525" s="1" t="n">
         <v>354680</v>
       </c>
-      <c r="B525" s="0" t="s">
+      <c r="B525" s="1" t="s">
         <v>526</v>
       </c>
       <c r="C525" s="2" t="n">
@@ -7970,7 +7961,7 @@
       <c r="A526" s="1" t="n">
         <v>354690</v>
       </c>
-      <c r="B526" s="0" t="s">
+      <c r="B526" s="1" t="s">
         <v>527</v>
       </c>
       <c r="C526" s="2" t="n">
@@ -7981,7 +7972,7 @@
       <c r="A527" s="1" t="n">
         <v>354700</v>
       </c>
-      <c r="B527" s="0" t="s">
+      <c r="B527" s="1" t="s">
         <v>528</v>
       </c>
       <c r="C527" s="2" t="n">
@@ -7992,7 +7983,7 @@
       <c r="A528" s="1" t="n">
         <v>354710</v>
       </c>
-      <c r="B528" s="0" t="s">
+      <c r="B528" s="1" t="s">
         <v>529</v>
       </c>
       <c r="C528" s="2" t="n">
@@ -8003,7 +7994,7 @@
       <c r="A529" s="1" t="n">
         <v>354720</v>
       </c>
-      <c r="B529" s="0" t="s">
+      <c r="B529" s="1" t="s">
         <v>530</v>
       </c>
       <c r="C529" s="2" t="n">
@@ -8014,7 +8005,7 @@
       <c r="A530" s="1" t="n">
         <v>354730</v>
       </c>
-      <c r="B530" s="0" t="s">
+      <c r="B530" s="1" t="s">
         <v>531</v>
       </c>
       <c r="C530" s="2" t="n">
@@ -8025,7 +8016,7 @@
       <c r="A531" s="1" t="n">
         <v>354740</v>
       </c>
-      <c r="B531" s="0" t="s">
+      <c r="B531" s="1" t="s">
         <v>532</v>
       </c>
       <c r="C531" s="2" t="n">
@@ -8036,7 +8027,7 @@
       <c r="A532" s="1" t="n">
         <v>354750</v>
       </c>
-      <c r="B532" s="0" t="s">
+      <c r="B532" s="1" t="s">
         <v>533</v>
       </c>
       <c r="C532" s="2" t="n">
@@ -8047,7 +8038,7 @@
       <c r="A533" s="1" t="n">
         <v>354760</v>
       </c>
-      <c r="B533" s="0" t="s">
+      <c r="B533" s="1" t="s">
         <v>534</v>
       </c>
       <c r="C533" s="2" t="n">
@@ -8058,7 +8049,7 @@
       <c r="A534" s="1" t="n">
         <v>354765</v>
       </c>
-      <c r="B534" s="0" t="s">
+      <c r="B534" s="1" t="s">
         <v>535</v>
       </c>
       <c r="C534" s="2" t="n">
@@ -8069,7 +8060,7 @@
       <c r="A535" s="1" t="n">
         <v>354770</v>
       </c>
-      <c r="B535" s="0" t="s">
+      <c r="B535" s="1" t="s">
         <v>536</v>
       </c>
       <c r="C535" s="2" t="n">
@@ -8080,7 +8071,7 @@
       <c r="A536" s="1" t="n">
         <v>354780</v>
       </c>
-      <c r="B536" s="0" t="s">
+      <c r="B536" s="1" t="s">
         <v>537</v>
       </c>
       <c r="C536" s="2" t="n">
@@ -8091,7 +8082,7 @@
       <c r="A537" s="1" t="n">
         <v>354790</v>
       </c>
-      <c r="B537" s="0" t="s">
+      <c r="B537" s="1" t="s">
         <v>538</v>
       </c>
       <c r="C537" s="2" t="n">
@@ -8102,7 +8093,7 @@
       <c r="A538" s="1" t="n">
         <v>354800</v>
       </c>
-      <c r="B538" s="0" t="s">
+      <c r="B538" s="1" t="s">
         <v>539</v>
       </c>
       <c r="C538" s="2" t="n">
@@ -8113,7 +8104,7 @@
       <c r="A539" s="1" t="n">
         <v>354805</v>
       </c>
-      <c r="B539" s="0" t="s">
+      <c r="B539" s="1" t="s">
         <v>540</v>
       </c>
       <c r="C539" s="2" t="n">
@@ -8124,7 +8115,7 @@
       <c r="A540" s="1" t="n">
         <v>354810</v>
       </c>
-      <c r="B540" s="0" t="s">
+      <c r="B540" s="1" t="s">
         <v>541</v>
       </c>
       <c r="C540" s="2" t="n">
@@ -8135,7 +8126,7 @@
       <c r="A541" s="1" t="n">
         <v>354820</v>
       </c>
-      <c r="B541" s="0" t="s">
+      <c r="B541" s="1" t="s">
         <v>542</v>
       </c>
       <c r="C541" s="2" t="n">
@@ -8146,7 +8137,7 @@
       <c r="A542" s="1" t="n">
         <v>354830</v>
       </c>
-      <c r="B542" s="0" t="s">
+      <c r="B542" s="1" t="s">
         <v>543</v>
       </c>
       <c r="C542" s="2" t="n">
@@ -8157,7 +8148,7 @@
       <c r="A543" s="1" t="n">
         <v>354840</v>
       </c>
-      <c r="B543" s="0" t="s">
+      <c r="B543" s="1" t="s">
         <v>544</v>
       </c>
       <c r="C543" s="2" t="n">
@@ -8168,7 +8159,7 @@
       <c r="A544" s="1" t="n">
         <v>354850</v>
       </c>
-      <c r="B544" s="0" t="s">
+      <c r="B544" s="1" t="s">
         <v>545</v>
       </c>
       <c r="C544" s="2" t="n">
@@ -8179,7 +8170,7 @@
       <c r="A545" s="1" t="n">
         <v>354860</v>
       </c>
-      <c r="B545" s="0" t="s">
+      <c r="B545" s="1" t="s">
         <v>546</v>
       </c>
       <c r="C545" s="2" t="n">
@@ -8190,7 +8181,7 @@
       <c r="A546" s="1" t="n">
         <v>354870</v>
       </c>
-      <c r="B546" s="0" t="s">
+      <c r="B546" s="1" t="s">
         <v>547</v>
       </c>
       <c r="C546" s="2" t="n">
@@ -8201,7 +8192,7 @@
       <c r="A547" s="1" t="n">
         <v>354880</v>
       </c>
-      <c r="B547" s="0" t="s">
+      <c r="B547" s="1" t="s">
         <v>548</v>
       </c>
       <c r="C547" s="2" t="n">
@@ -8212,7 +8203,7 @@
       <c r="A548" s="1" t="n">
         <v>354890</v>
       </c>
-      <c r="B548" s="0" t="s">
+      <c r="B548" s="1" t="s">
         <v>549</v>
       </c>
       <c r="C548" s="2" t="n">
@@ -8223,7 +8214,7 @@
       <c r="A549" s="1" t="n">
         <v>354900</v>
       </c>
-      <c r="B549" s="0" t="s">
+      <c r="B549" s="1" t="s">
         <v>550</v>
       </c>
       <c r="C549" s="2" t="n">
@@ -8234,7 +8225,7 @@
       <c r="A550" s="1" t="n">
         <v>354910</v>
       </c>
-      <c r="B550" s="0" t="s">
+      <c r="B550" s="1" t="s">
         <v>551</v>
       </c>
       <c r="C550" s="2" t="n">
@@ -8245,7 +8236,7 @@
       <c r="A551" s="1" t="n">
         <v>354920</v>
       </c>
-      <c r="B551" s="0" t="s">
+      <c r="B551" s="1" t="s">
         <v>552</v>
       </c>
       <c r="C551" s="2" t="n">
@@ -8256,7 +8247,7 @@
       <c r="A552" s="1" t="n">
         <v>354925</v>
       </c>
-      <c r="B552" s="0" t="s">
+      <c r="B552" s="1" t="s">
         <v>553</v>
       </c>
       <c r="C552" s="2" t="n">
@@ -8267,7 +8258,7 @@
       <c r="A553" s="1" t="n">
         <v>354930</v>
       </c>
-      <c r="B553" s="0" t="s">
+      <c r="B553" s="1" t="s">
         <v>554</v>
       </c>
       <c r="C553" s="2" t="n">
@@ -8278,7 +8269,7 @@
       <c r="A554" s="1" t="n">
         <v>354940</v>
       </c>
-      <c r="B554" s="0" t="s">
+      <c r="B554" s="1" t="s">
         <v>555</v>
       </c>
       <c r="C554" s="2" t="n">
@@ -8289,7 +8280,7 @@
       <c r="A555" s="1" t="n">
         <v>354950</v>
       </c>
-      <c r="B555" s="0" t="s">
+      <c r="B555" s="1" t="s">
         <v>556</v>
       </c>
       <c r="C555" s="2" t="n">
@@ -8300,7 +8291,7 @@
       <c r="A556" s="1" t="n">
         <v>354960</v>
       </c>
-      <c r="B556" s="0" t="s">
+      <c r="B556" s="1" t="s">
         <v>557</v>
       </c>
       <c r="C556" s="2" t="n">
@@ -8311,7 +8302,7 @@
       <c r="A557" s="1" t="n">
         <v>354970</v>
       </c>
-      <c r="B557" s="0" t="s">
+      <c r="B557" s="1" t="s">
         <v>558</v>
       </c>
       <c r="C557" s="2" t="n">
@@ -8322,7 +8313,7 @@
       <c r="A558" s="1" t="n">
         <v>354980</v>
       </c>
-      <c r="B558" s="0" t="s">
+      <c r="B558" s="1" t="s">
         <v>559</v>
       </c>
       <c r="C558" s="2" t="n">
@@ -8333,7 +8324,7 @@
       <c r="A559" s="1" t="n">
         <v>354990</v>
       </c>
-      <c r="B559" s="0" t="s">
+      <c r="B559" s="1" t="s">
         <v>560</v>
       </c>
       <c r="C559" s="2" t="n">
@@ -8344,7 +8335,7 @@
       <c r="A560" s="1" t="n">
         <v>354995</v>
       </c>
-      <c r="B560" s="0" t="s">
+      <c r="B560" s="1" t="s">
         <v>561</v>
       </c>
       <c r="C560" s="2" t="n">
@@ -8355,7 +8346,7 @@
       <c r="A561" s="1" t="n">
         <v>355000</v>
       </c>
-      <c r="B561" s="0" t="s">
+      <c r="B561" s="1" t="s">
         <v>562</v>
       </c>
       <c r="C561" s="2" t="n">
@@ -8366,7 +8357,7 @@
       <c r="A562" s="1" t="n">
         <v>355010</v>
       </c>
-      <c r="B562" s="0" t="s">
+      <c r="B562" s="1" t="s">
         <v>563</v>
       </c>
       <c r="C562" s="2" t="n">
@@ -8377,7 +8368,7 @@
       <c r="A563" s="1" t="n">
         <v>355020</v>
       </c>
-      <c r="B563" s="0" t="s">
+      <c r="B563" s="1" t="s">
         <v>564</v>
       </c>
       <c r="C563" s="2" t="n">
@@ -8388,7 +8379,7 @@
       <c r="A564" s="1" t="n">
         <v>355030</v>
       </c>
-      <c r="B564" s="0" t="s">
+      <c r="B564" s="1" t="s">
         <v>565</v>
       </c>
       <c r="C564" s="2" t="n">
@@ -8399,7 +8390,7 @@
       <c r="A565" s="1" t="n">
         <v>355040</v>
       </c>
-      <c r="B565" s="0" t="s">
+      <c r="B565" s="1" t="s">
         <v>566</v>
       </c>
       <c r="C565" s="2" t="n">
@@ -8410,7 +8401,7 @@
       <c r="A566" s="1" t="n">
         <v>355050</v>
       </c>
-      <c r="B566" s="0" t="s">
+      <c r="B566" s="1" t="s">
         <v>567</v>
       </c>
       <c r="C566" s="2" t="n">
@@ -8421,7 +8412,7 @@
       <c r="A567" s="1" t="n">
         <v>355060</v>
       </c>
-      <c r="B567" s="0" t="s">
+      <c r="B567" s="1" t="s">
         <v>568</v>
       </c>
       <c r="C567" s="2" t="n">
@@ -8432,7 +8423,7 @@
       <c r="A568" s="1" t="n">
         <v>355070</v>
       </c>
-      <c r="B568" s="0" t="s">
+      <c r="B568" s="1" t="s">
         <v>569</v>
       </c>
       <c r="C568" s="2" t="n">
@@ -8443,7 +8434,7 @@
       <c r="A569" s="1" t="n">
         <v>355080</v>
       </c>
-      <c r="B569" s="0" t="s">
+      <c r="B569" s="1" t="s">
         <v>570</v>
       </c>
       <c r="C569" s="2" t="n">
@@ -8454,7 +8445,7 @@
       <c r="A570" s="1" t="n">
         <v>355090</v>
       </c>
-      <c r="B570" s="0" t="s">
+      <c r="B570" s="1" t="s">
         <v>571</v>
       </c>
       <c r="C570" s="2" t="n">
@@ -8465,7 +8456,7 @@
       <c r="A571" s="1" t="n">
         <v>355100</v>
       </c>
-      <c r="B571" s="0" t="s">
+      <c r="B571" s="1" t="s">
         <v>572</v>
       </c>
       <c r="C571" s="2" t="n">
@@ -8476,7 +8467,7 @@
       <c r="A572" s="1" t="n">
         <v>355110</v>
       </c>
-      <c r="B572" s="0" t="s">
+      <c r="B572" s="1" t="s">
         <v>573</v>
       </c>
       <c r="C572" s="2" t="n">
@@ -8487,7 +8478,7 @@
       <c r="A573" s="1" t="n">
         <v>355120</v>
       </c>
-      <c r="B573" s="0" t="s">
+      <c r="B573" s="1" t="s">
         <v>574</v>
       </c>
       <c r="C573" s="2" t="n">
@@ -8498,7 +8489,7 @@
       <c r="A574" s="1" t="n">
         <v>355130</v>
       </c>
-      <c r="B574" s="0" t="s">
+      <c r="B574" s="1" t="s">
         <v>575</v>
       </c>
       <c r="C574" s="2" t="n">
@@ -8509,7 +8500,7 @@
       <c r="A575" s="1" t="n">
         <v>355140</v>
       </c>
-      <c r="B575" s="0" t="s">
+      <c r="B575" s="1" t="s">
         <v>576</v>
       </c>
       <c r="C575" s="2" t="n">
@@ -8520,7 +8511,7 @@
       <c r="A576" s="1" t="n">
         <v>355150</v>
       </c>
-      <c r="B576" s="0" t="s">
+      <c r="B576" s="1" t="s">
         <v>577</v>
       </c>
       <c r="C576" s="2" t="n">
@@ -8531,7 +8522,7 @@
       <c r="A577" s="1" t="n">
         <v>355160</v>
       </c>
-      <c r="B577" s="0" t="s">
+      <c r="B577" s="1" t="s">
         <v>578</v>
       </c>
       <c r="C577" s="2" t="n">
@@ -8542,7 +8533,7 @@
       <c r="A578" s="1" t="n">
         <v>355170</v>
       </c>
-      <c r="B578" s="0" t="s">
+      <c r="B578" s="1" t="s">
         <v>579</v>
       </c>
       <c r="C578" s="2" t="n">
@@ -8553,7 +8544,7 @@
       <c r="A579" s="1" t="n">
         <v>355180</v>
       </c>
-      <c r="B579" s="0" t="s">
+      <c r="B579" s="1" t="s">
         <v>580</v>
       </c>
       <c r="C579" s="2" t="n">
@@ -8564,7 +8555,7 @@
       <c r="A580" s="1" t="n">
         <v>355190</v>
       </c>
-      <c r="B580" s="0" t="s">
+      <c r="B580" s="1" t="s">
         <v>581</v>
       </c>
       <c r="C580" s="2" t="n">
@@ -8575,7 +8566,7 @@
       <c r="A581" s="1" t="n">
         <v>355200</v>
       </c>
-      <c r="B581" s="0" t="s">
+      <c r="B581" s="1" t="s">
         <v>582</v>
       </c>
       <c r="C581" s="2" t="n">
@@ -8586,7 +8577,7 @@
       <c r="A582" s="1" t="n">
         <v>355210</v>
       </c>
-      <c r="B582" s="0" t="s">
+      <c r="B582" s="1" t="s">
         <v>583</v>
       </c>
       <c r="C582" s="2" t="n">
@@ -8597,7 +8588,7 @@
       <c r="A583" s="1" t="n">
         <v>355220</v>
       </c>
-      <c r="B583" s="0" t="s">
+      <c r="B583" s="1" t="s">
         <v>584</v>
       </c>
       <c r="C583" s="2" t="n">
@@ -8608,7 +8599,7 @@
       <c r="A584" s="1" t="n">
         <v>355230</v>
       </c>
-      <c r="B584" s="0" t="s">
+      <c r="B584" s="1" t="s">
         <v>585</v>
       </c>
       <c r="C584" s="2" t="n">
@@ -8619,7 +8610,7 @@
       <c r="A585" s="1" t="n">
         <v>355240</v>
       </c>
-      <c r="B585" s="0" t="s">
+      <c r="B585" s="1" t="s">
         <v>586</v>
       </c>
       <c r="C585" s="2" t="n">
@@ -8630,7 +8621,7 @@
       <c r="A586" s="1" t="n">
         <v>355250</v>
       </c>
-      <c r="B586" s="0" t="s">
+      <c r="B586" s="1" t="s">
         <v>587</v>
       </c>
       <c r="C586" s="2" t="n">
@@ -8641,7 +8632,7 @@
       <c r="A587" s="1" t="n">
         <v>355255</v>
       </c>
-      <c r="B587" s="0" t="s">
+      <c r="B587" s="1" t="s">
         <v>588</v>
       </c>
       <c r="C587" s="2" t="n">
@@ -8652,7 +8643,7 @@
       <c r="A588" s="1" t="n">
         <v>355260</v>
       </c>
-      <c r="B588" s="0" t="s">
+      <c r="B588" s="1" t="s">
         <v>589</v>
       </c>
       <c r="C588" s="2" t="n">
@@ -8663,7 +8654,7 @@
       <c r="A589" s="1" t="n">
         <v>355270</v>
       </c>
-      <c r="B589" s="0" t="s">
+      <c r="B589" s="1" t="s">
         <v>590</v>
       </c>
       <c r="C589" s="2" t="n">
@@ -8674,7 +8665,7 @@
       <c r="A590" s="1" t="n">
         <v>355280</v>
       </c>
-      <c r="B590" s="0" t="s">
+      <c r="B590" s="1" t="s">
         <v>591</v>
       </c>
       <c r="C590" s="2" t="n">
@@ -8685,7 +8676,7 @@
       <c r="A591" s="1" t="n">
         <v>355290</v>
       </c>
-      <c r="B591" s="0" t="s">
+      <c r="B591" s="1" t="s">
         <v>592</v>
       </c>
       <c r="C591" s="2" t="n">
@@ -8696,7 +8687,7 @@
       <c r="A592" s="1" t="n">
         <v>355300</v>
       </c>
-      <c r="B592" s="0" t="s">
+      <c r="B592" s="1" t="s">
         <v>593</v>
       </c>
       <c r="C592" s="2" t="n">
@@ -8707,7 +8698,7 @@
       <c r="A593" s="1" t="n">
         <v>355310</v>
       </c>
-      <c r="B593" s="0" t="s">
+      <c r="B593" s="1" t="s">
         <v>594</v>
       </c>
       <c r="C593" s="2" t="n">
@@ -8718,7 +8709,7 @@
       <c r="A594" s="1" t="n">
         <v>355320</v>
       </c>
-      <c r="B594" s="0" t="s">
+      <c r="B594" s="1" t="s">
         <v>595</v>
       </c>
       <c r="C594" s="2" t="n">
@@ -8729,7 +8720,7 @@
       <c r="A595" s="1" t="n">
         <v>355330</v>
       </c>
-      <c r="B595" s="0" t="s">
+      <c r="B595" s="1" t="s">
         <v>596</v>
       </c>
       <c r="C595" s="2" t="n">
@@ -8740,7 +8731,7 @@
       <c r="A596" s="1" t="n">
         <v>355340</v>
       </c>
-      <c r="B596" s="0" t="s">
+      <c r="B596" s="1" t="s">
         <v>597</v>
       </c>
       <c r="C596" s="2" t="n">
@@ -8751,7 +8742,7 @@
       <c r="A597" s="1" t="n">
         <v>355350</v>
       </c>
-      <c r="B597" s="0" t="s">
+      <c r="B597" s="1" t="s">
         <v>598</v>
       </c>
       <c r="C597" s="2" t="n">
@@ -8762,7 +8753,7 @@
       <c r="A598" s="1" t="n">
         <v>355360</v>
       </c>
-      <c r="B598" s="0" t="s">
+      <c r="B598" s="1" t="s">
         <v>599</v>
       </c>
       <c r="C598" s="2" t="n">
@@ -8773,7 +8764,7 @@
       <c r="A599" s="1" t="n">
         <v>355365</v>
       </c>
-      <c r="B599" s="0" t="s">
+      <c r="B599" s="1" t="s">
         <v>600</v>
       </c>
       <c r="C599" s="2" t="n">
@@ -8784,7 +8775,7 @@
       <c r="A600" s="1" t="n">
         <v>355370</v>
       </c>
-      <c r="B600" s="0" t="s">
+      <c r="B600" s="1" t="s">
         <v>601</v>
       </c>
       <c r="C600" s="2" t="n">
@@ -8795,7 +8786,7 @@
       <c r="A601" s="1" t="n">
         <v>355380</v>
       </c>
-      <c r="B601" s="0" t="s">
+      <c r="B601" s="1" t="s">
         <v>602</v>
       </c>
       <c r="C601" s="2" t="n">
@@ -8806,7 +8797,7 @@
       <c r="A602" s="1" t="n">
         <v>355385</v>
       </c>
-      <c r="B602" s="0" t="s">
+      <c r="B602" s="1" t="s">
         <v>603</v>
       </c>
       <c r="C602" s="2" t="n">
@@ -8817,7 +8808,7 @@
       <c r="A603" s="1" t="n">
         <v>355390</v>
       </c>
-      <c r="B603" s="0" t="s">
+      <c r="B603" s="1" t="s">
         <v>604</v>
       </c>
       <c r="C603" s="2" t="n">
@@ -8828,7 +8819,7 @@
       <c r="A604" s="1" t="n">
         <v>355395</v>
       </c>
-      <c r="B604" s="0" t="s">
+      <c r="B604" s="1" t="s">
         <v>605</v>
       </c>
       <c r="C604" s="2" t="n">
@@ -8839,7 +8830,7 @@
       <c r="A605" s="1" t="n">
         <v>355400</v>
       </c>
-      <c r="B605" s="0" t="s">
+      <c r="B605" s="1" t="s">
         <v>606</v>
       </c>
       <c r="C605" s="2" t="n">
@@ -8850,7 +8841,7 @@
       <c r="A606" s="1" t="n">
         <v>355410</v>
       </c>
-      <c r="B606" s="0" t="s">
+      <c r="B606" s="1" t="s">
         <v>607</v>
       </c>
       <c r="C606" s="2" t="n">
@@ -8861,7 +8852,7 @@
       <c r="A607" s="1" t="n">
         <v>355420</v>
       </c>
-      <c r="B607" s="0" t="s">
+      <c r="B607" s="1" t="s">
         <v>608</v>
       </c>
       <c r="C607" s="2" t="n">
@@ -8872,7 +8863,7 @@
       <c r="A608" s="1" t="n">
         <v>355430</v>
       </c>
-      <c r="B608" s="0" t="s">
+      <c r="B608" s="1" t="s">
         <v>609</v>
       </c>
       <c r="C608" s="2" t="n">
@@ -8883,7 +8874,7 @@
       <c r="A609" s="1" t="n">
         <v>355440</v>
       </c>
-      <c r="B609" s="0" t="s">
+      <c r="B609" s="1" t="s">
         <v>610</v>
       </c>
       <c r="C609" s="2" t="n">
@@ -8894,7 +8885,7 @@
       <c r="A610" s="1" t="n">
         <v>355450</v>
       </c>
-      <c r="B610" s="0" t="s">
+      <c r="B610" s="1" t="s">
         <v>611</v>
       </c>
       <c r="C610" s="2" t="n">
@@ -8905,7 +8896,7 @@
       <c r="A611" s="1" t="n">
         <v>355460</v>
       </c>
-      <c r="B611" s="0" t="s">
+      <c r="B611" s="1" t="s">
         <v>612</v>
       </c>
       <c r="C611" s="2" t="n">
@@ -8916,7 +8907,7 @@
       <c r="A612" s="1" t="n">
         <v>355465</v>
       </c>
-      <c r="B612" s="0" t="s">
+      <c r="B612" s="1" t="s">
         <v>613</v>
       </c>
       <c r="C612" s="2" t="n">
@@ -8927,7 +8918,7 @@
       <c r="A613" s="1" t="n">
         <v>355470</v>
       </c>
-      <c r="B613" s="0" t="s">
+      <c r="B613" s="1" t="s">
         <v>614</v>
       </c>
       <c r="C613" s="2" t="n">
@@ -8938,7 +8929,7 @@
       <c r="A614" s="1" t="n">
         <v>355475</v>
       </c>
-      <c r="B614" s="0" t="s">
+      <c r="B614" s="1" t="s">
         <v>615</v>
       </c>
       <c r="C614" s="2" t="n">
@@ -8949,7 +8940,7 @@
       <c r="A615" s="1" t="n">
         <v>355480</v>
       </c>
-      <c r="B615" s="0" t="s">
+      <c r="B615" s="1" t="s">
         <v>616</v>
       </c>
       <c r="C615" s="2" t="n">
@@ -8960,7 +8951,7 @@
       <c r="A616" s="1" t="n">
         <v>355490</v>
       </c>
-      <c r="B616" s="0" t="s">
+      <c r="B616" s="1" t="s">
         <v>617</v>
       </c>
       <c r="C616" s="2" t="n">
@@ -8971,7 +8962,7 @@
       <c r="A617" s="1" t="n">
         <v>355495</v>
       </c>
-      <c r="B617" s="0" t="s">
+      <c r="B617" s="1" t="s">
         <v>618</v>
       </c>
       <c r="C617" s="2" t="n">
@@ -8982,7 +8973,7 @@
       <c r="A618" s="1" t="n">
         <v>355500</v>
       </c>
-      <c r="B618" s="0" t="s">
+      <c r="B618" s="1" t="s">
         <v>619</v>
       </c>
       <c r="C618" s="2" t="n">
@@ -8993,7 +8984,7 @@
       <c r="A619" s="1" t="n">
         <v>355510</v>
       </c>
-      <c r="B619" s="0" t="s">
+      <c r="B619" s="1" t="s">
         <v>620</v>
       </c>
       <c r="C619" s="2" t="n">
@@ -9004,7 +8995,7 @@
       <c r="A620" s="1" t="n">
         <v>355520</v>
       </c>
-      <c r="B620" s="0" t="s">
+      <c r="B620" s="1" t="s">
         <v>621</v>
       </c>
       <c r="C620" s="2" t="n">
@@ -9015,7 +9006,7 @@
       <c r="A621" s="1" t="n">
         <v>355530</v>
       </c>
-      <c r="B621" s="0" t="s">
+      <c r="B621" s="1" t="s">
         <v>622</v>
       </c>
       <c r="C621" s="2" t="n">
@@ -9026,7 +9017,7 @@
       <c r="A622" s="1" t="n">
         <v>355535</v>
       </c>
-      <c r="B622" s="0" t="s">
+      <c r="B622" s="1" t="s">
         <v>623</v>
       </c>
       <c r="C622" s="2" t="n">
@@ -9037,7 +9028,7 @@
       <c r="A623" s="1" t="n">
         <v>355540</v>
       </c>
-      <c r="B623" s="0" t="s">
+      <c r="B623" s="1" t="s">
         <v>624</v>
       </c>
       <c r="C623" s="2" t="n">
@@ -9048,7 +9039,7 @@
       <c r="A624" s="1" t="n">
         <v>355550</v>
       </c>
-      <c r="B624" s="0" t="s">
+      <c r="B624" s="1" t="s">
         <v>625</v>
       </c>
       <c r="C624" s="2" t="n">
@@ -9059,7 +9050,7 @@
       <c r="A625" s="1" t="n">
         <v>355560</v>
       </c>
-      <c r="B625" s="0" t="s">
+      <c r="B625" s="1" t="s">
         <v>626</v>
       </c>
       <c r="C625" s="2" t="n">
@@ -9070,7 +9061,7 @@
       <c r="A626" s="1" t="n">
         <v>355570</v>
       </c>
-      <c r="B626" s="0" t="s">
+      <c r="B626" s="1" t="s">
         <v>627</v>
       </c>
       <c r="C626" s="2" t="n">
@@ -9081,7 +9072,7 @@
       <c r="A627" s="1" t="n">
         <v>355580</v>
       </c>
-      <c r="B627" s="0" t="s">
+      <c r="B627" s="1" t="s">
         <v>628</v>
       </c>
       <c r="C627" s="2" t="n">
@@ -9092,7 +9083,7 @@
       <c r="A628" s="1" t="n">
         <v>355590</v>
       </c>
-      <c r="B628" s="0" t="s">
+      <c r="B628" s="1" t="s">
         <v>629</v>
       </c>
       <c r="C628" s="2" t="n">
@@ -9103,7 +9094,7 @@
       <c r="A629" s="1" t="n">
         <v>355600</v>
       </c>
-      <c r="B629" s="0" t="s">
+      <c r="B629" s="1" t="s">
         <v>630</v>
       </c>
       <c r="C629" s="2" t="n">
@@ -9114,7 +9105,7 @@
       <c r="A630" s="1" t="n">
         <v>355610</v>
       </c>
-      <c r="B630" s="0" t="s">
+      <c r="B630" s="1" t="s">
         <v>631</v>
       </c>
       <c r="C630" s="2" t="n">
@@ -9125,7 +9116,7 @@
       <c r="A631" s="1" t="n">
         <v>355620</v>
       </c>
-      <c r="B631" s="0" t="s">
+      <c r="B631" s="1" t="s">
         <v>632</v>
       </c>
       <c r="C631" s="2" t="n">
@@ -9136,7 +9127,7 @@
       <c r="A632" s="1" t="n">
         <v>355630</v>
       </c>
-      <c r="B632" s="0" t="s">
+      <c r="B632" s="1" t="s">
         <v>633</v>
       </c>
       <c r="C632" s="2" t="n">
@@ -9147,7 +9138,7 @@
       <c r="A633" s="1" t="n">
         <v>355635</v>
       </c>
-      <c r="B633" s="0" t="s">
+      <c r="B633" s="1" t="s">
         <v>634</v>
       </c>
       <c r="C633" s="2" t="n">
@@ -9158,7 +9149,7 @@
       <c r="A634" s="1" t="n">
         <v>355640</v>
       </c>
-      <c r="B634" s="0" t="s">
+      <c r="B634" s="1" t="s">
         <v>635</v>
       </c>
       <c r="C634" s="2" t="n">
@@ -9169,7 +9160,7 @@
       <c r="A635" s="1" t="n">
         <v>355645</v>
       </c>
-      <c r="B635" s="0" t="s">
+      <c r="B635" s="1" t="s">
         <v>636</v>
       </c>
       <c r="C635" s="2" t="n">
@@ -9180,7 +9171,7 @@
       <c r="A636" s="1" t="n">
         <v>355650</v>
       </c>
-      <c r="B636" s="0" t="s">
+      <c r="B636" s="1" t="s">
         <v>637</v>
       </c>
       <c r="C636" s="2" t="n">
@@ -9191,7 +9182,7 @@
       <c r="A637" s="1" t="n">
         <v>355660</v>
       </c>
-      <c r="B637" s="0" t="s">
+      <c r="B637" s="1" t="s">
         <v>638</v>
       </c>
       <c r="C637" s="2" t="n">
@@ -9202,7 +9193,7 @@
       <c r="A638" s="1" t="n">
         <v>355670</v>
       </c>
-      <c r="B638" s="0" t="s">
+      <c r="B638" s="1" t="s">
         <v>639</v>
       </c>
       <c r="C638" s="2" t="n">
@@ -9213,7 +9204,7 @@
       <c r="A639" s="1" t="n">
         <v>355680</v>
       </c>
-      <c r="B639" s="0" t="s">
+      <c r="B639" s="1" t="s">
         <v>640</v>
       </c>
       <c r="C639" s="2" t="n">
@@ -9224,7 +9215,7 @@
       <c r="A640" s="1" t="n">
         <v>355690</v>
       </c>
-      <c r="B640" s="0" t="s">
+      <c r="B640" s="1" t="s">
         <v>641</v>
       </c>
       <c r="C640" s="2" t="n">
@@ -9235,7 +9226,7 @@
       <c r="A641" s="1" t="n">
         <v>355695</v>
       </c>
-      <c r="B641" s="0" t="s">
+      <c r="B641" s="1" t="s">
         <v>642</v>
       </c>
       <c r="C641" s="2" t="n">
@@ -9246,7 +9237,7 @@
       <c r="A642" s="1" t="n">
         <v>355700</v>
       </c>
-      <c r="B642" s="0" t="s">
+      <c r="B642" s="1" t="s">
         <v>643</v>
       </c>
       <c r="C642" s="2" t="n">
@@ -9257,7 +9248,7 @@
       <c r="A643" s="1" t="n">
         <v>355710</v>
       </c>
-      <c r="B643" s="0" t="s">
+      <c r="B643" s="1" t="s">
         <v>644</v>
       </c>
       <c r="C643" s="2" t="n">
@@ -9268,7 +9259,7 @@
       <c r="A644" s="1" t="n">
         <v>355715</v>
       </c>
-      <c r="B644" s="0" t="s">
+      <c r="B644" s="1" t="s">
         <v>645</v>
       </c>
       <c r="C644" s="2" t="n">
@@ -9279,7 +9270,7 @@
       <c r="A645" s="1" t="n">
         <v>355720</v>
       </c>
-      <c r="B645" s="0" t="s">
+      <c r="B645" s="1" t="s">
         <v>646</v>
       </c>
       <c r="C645" s="2" t="n">
@@ -9290,27 +9281,11 @@
       <c r="A646" s="1" t="n">
         <v>355730</v>
       </c>
-      <c r="B646" s="0" t="s">
+      <c r="B646" s="1" t="s">
         <v>647</v>
       </c>
       <c r="C646" s="2" t="n">
         <v>10935</v>
-      </c>
-    </row>
-    <row r="647" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A647" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="C647" s="2" t="n">
-        <v>44785082.6</v>
-      </c>
-    </row>
-    <row r="648" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A648" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="B648" s="0" t="s">
-        <v>650</v>
       </c>
     </row>
   </sheetData>
